--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3507000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3336000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3304000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3152000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3111000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2957000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2926000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2885000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3054000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2959000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3029000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2866000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2931000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2820000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2766000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2291000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2787000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2699000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2616000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2709000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2415000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2625000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2574000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>436000</v>
+      </c>
+      <c r="E9" s="3">
         <v>426000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>403000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>379000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>389000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>383000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>374000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>344000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>359000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>368000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>357000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>359000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>364000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>360000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>342000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>344000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>358000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>345000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>338000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>342000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>343000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>337000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>359000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>296000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>307000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>309000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>312000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>305000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>309000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3071000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2910000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2901000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2773000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2722000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2574000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2552000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2541000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2695000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2591000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2672000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2507000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2567000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2460000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2424000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1947000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2429000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2354000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2278000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2367000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2072000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2288000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2215000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1314,8 +1333,8 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1332,50 +1351,53 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>10000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>5000</v>
       </c>
       <c r="AB14" s="3">
         <v>5000</v>
       </c>
       <c r="AC14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AD14" s="3">
         <v>2000</v>
       </c>
       <c r="AE14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF14" s="3">
         <v>25000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3013000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2976000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2912000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2753000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2789000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2980000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2671000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2502000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2696000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2617000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2538000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2460000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2425000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2538000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2553000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2349000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2421000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2540000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2240000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2256000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2495000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2189000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2209000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>494000</v>
+      </c>
+      <c r="E18" s="3">
         <v>360000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>392000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>399000</v>
       </c>
-      <c r="G18" s="3">
-        <v>322000</v>
-      </c>
       <c r="H18" s="3">
+        <v>311000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-23000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>255000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>383000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>358000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>342000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>491000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>406000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>506000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>282000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>213000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-58000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>366000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>159000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>376000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>453000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-80000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>436000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>365000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>381000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>447000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>228000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>410000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>386000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>357000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1747,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1807,100 +1840,106 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>523000</v>
+      </c>
+      <c r="E21" s="3">
         <v>376000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>408000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>411000</v>
       </c>
-      <c r="G21" s="3">
-        <v>335000</v>
-      </c>
       <c r="H21" s="3">
+        <v>324000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-10000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>267000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>396000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>371000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>356000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>504000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>420000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>520000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>297000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>228000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-42000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>382000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>175000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>393000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>472000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-60000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>454000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>386000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>401000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>469000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>251000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>432000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>407000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>377000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1908,10 +1947,10 @@
         <v>34000</v>
       </c>
       <c r="E22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F22" s="3">
         <v>31000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>28000</v>
       </c>
       <c r="G22" s="3">
         <v>28000</v>
@@ -1932,19 +1971,19 @@
         <v>28000</v>
       </c>
       <c r="M22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="N22" s="3">
         <v>29000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>28000</v>
       </c>
       <c r="O22" s="3">
         <v>28000</v>
       </c>
       <c r="P22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>32000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>31000</v>
       </c>
       <c r="R22" s="3">
         <v>31000</v>
@@ -1953,10 +1992,10 @@
         <v>31000</v>
       </c>
       <c r="T22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="U22" s="3">
         <v>32000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>34000</v>
       </c>
       <c r="V22" s="3">
         <v>34000</v>
@@ -1968,215 +2007,224 @@
         <v>34000</v>
       </c>
       <c r="Y22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="Z22" s="3">
         <v>35000</v>
       </c>
       <c r="AA22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>37000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>41000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>40000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>43000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>40000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>460000</v>
+      </c>
+      <c r="E23" s="3">
         <v>326000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>361000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>371000</v>
       </c>
-      <c r="G23" s="3">
-        <v>294000</v>
-      </c>
       <c r="H23" s="3">
+        <v>283000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-51000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>227000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>355000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>330000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>314000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>462000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>378000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>478000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>250000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>182000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-89000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>335000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>127000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>342000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>419000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-114000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>402000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>330000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>346000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>410000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>187000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>370000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>343000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>317000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E24" s="3">
         <v>68000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>78000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>74000</v>
       </c>
-      <c r="G24" s="3">
-        <v>46000</v>
-      </c>
       <c r="H24" s="3">
+        <v>44000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-9000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>37000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>60000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>94000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>66000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>91000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>37000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>31000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-28000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>62000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>64000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>77000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-30000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>66000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>60000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>55000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>104000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>43000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>98000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>83000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>76000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E26" s="3">
         <v>258000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>283000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>297000</v>
       </c>
-      <c r="G26" s="3">
-        <v>248000</v>
-      </c>
       <c r="H26" s="3">
+        <v>239000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-42000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>190000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>295000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>266000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>256000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>368000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>312000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>387000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>213000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>151000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-61000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>273000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>107000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>278000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>342000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-84000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>336000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>270000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>291000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>306000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>144000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>272000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>260000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>241000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E27" s="3">
         <v>258000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>283000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>297000</v>
       </c>
-      <c r="G27" s="3">
-        <v>248000</v>
-      </c>
       <c r="H27" s="3">
+        <v>239000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-42000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>190000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>295000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>266000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>256000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>368000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>312000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>387000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>213000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>151000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-61000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>273000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>107000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>278000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>342000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-84000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>336000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>270000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>291000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>306000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>144000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>272000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>260000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>241000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,8 +2659,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2617,11 +2677,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2629,14 +2689,17 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2885,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2911,100 +2980,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E33" s="3">
         <v>258000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>283000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>297000</v>
       </c>
-      <c r="G33" s="3">
-        <v>248000</v>
-      </c>
       <c r="H33" s="3">
+        <v>239000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-42000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>190000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>295000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>266000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>256000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>368000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>312000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>387000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>213000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>151000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-61000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>273000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>107000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>278000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>342000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-84000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>336000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>270000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>291000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>223000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>144000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>272000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>260000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>241000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E35" s="3">
         <v>258000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>283000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>297000</v>
       </c>
-      <c r="G35" s="3">
-        <v>248000</v>
-      </c>
       <c r="H35" s="3">
+        <v>239000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-42000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>190000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>295000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>266000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>256000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>368000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>312000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>387000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>213000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>151000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-61000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>273000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>107000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>278000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>342000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-84000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>336000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>270000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>291000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>223000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>144000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>272000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>260000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>241000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E41" s="3">
         <v>485000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>358000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>483000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>475000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>503000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>560000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>361000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>536000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>625000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>462000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>588000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>419000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>442000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>586000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>857000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>242000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>340000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>271000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>223000</v>
-      </c>
-      <c r="W41" s="3">
-        <v>310000</v>
       </c>
       <c r="X41" s="3">
         <v>310000</v>
       </c>
       <c r="Y41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="Z41" s="3">
         <v>288000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>282000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>355000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>283000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>225000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>299000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>271000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3442000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3211000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3521000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3126000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3158000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2986000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3210000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2892000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2945000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2799000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2954000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2652000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2607000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2527000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2755000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2502000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2481000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2504000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2690000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2476000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2365000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2642000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3910,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,218 +4005,227 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46562000</v>
+      </c>
+      <c r="E47" s="3">
         <v>43647000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>44435000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>44023000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43177000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>42137000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44280000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47106000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>50328000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>50236000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50265000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>48671000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50293000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>49006000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>47757000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>44086000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>47744000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>47535000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>46747000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>45639000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>44486000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>44929000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>45152000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E48" s="3">
         <v>257000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>246000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>232000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>226000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>229000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>227000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>225000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>226000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>234000</v>
       </c>
       <c r="M48" s="3">
         <v>234000</v>
       </c>
       <c r="N48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="O48" s="3">
         <v>244000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>451000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>256000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>264000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>271000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>502000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>516000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>525000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>547000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>324000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>332000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>347000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>346000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>326000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>325000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>336000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>324000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>310000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E49" s="3">
         <v>145000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>146000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>145000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>144000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>142000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>145000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>147000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>148000</v>
       </c>
       <c r="L49" s="3">
         <v>148000</v>
@@ -4130,58 +4240,61 @@
         <v>148000</v>
       </c>
       <c r="P49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>146000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>145000</v>
       </c>
       <c r="R49" s="3">
         <v>145000</v>
       </c>
       <c r="S49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="T49" s="3">
         <v>147000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>145000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>146000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>147000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>146000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>147000</v>
       </c>
       <c r="Y49" s="3">
         <v>147000</v>
       </c>
       <c r="Z49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>149000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>147000</v>
       </c>
       <c r="AC49" s="3">
         <v>147000</v>
       </c>
       <c r="AD49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>146000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>145000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1016000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1277000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1201000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1157000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1251000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1298000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>927000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>547000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>142000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>135000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>121000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>197000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>66000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>144000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>195000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>518000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>199000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>190000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>106000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>217000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>392000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>314000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>296000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>238000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>137000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>141000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>166000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>267000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>379000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>64711000</v>
+      </c>
+      <c r="E54" s="3">
         <v>61952000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>63088000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62055000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61000000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>60215000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>62229000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63792000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66639000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66522000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66207000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63713000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>64026000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62775000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62095000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58405000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>60612000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>60450000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59963000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58477000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>57152000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>57259000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>57858000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4800,25 +4930,28 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E58" s="3">
         <v>793000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>792000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>243000</v>
       </c>
       <c r="G58" s="3">
         <v>243000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
+      <c r="H58" s="3">
+        <v>243000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>8</v>
@@ -4835,8 +4968,8 @@
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4869,13 +5002,13 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>30000</v>
       </c>
       <c r="AA58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AB58" s="3">
         <v>150000</v>
@@ -4887,105 +5020,111 @@
         <v>150000</v>
       </c>
       <c r="AE58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20892000</v>
+      </c>
+      <c r="E59" s="3">
         <v>19443000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20644000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20557000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19854000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16649000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17215000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17880000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19245000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18775000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18877000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18091000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18716000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17998000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17592000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16479000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17195000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17217000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16486000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15808000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14780000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14894000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15077000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,100 +5215,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2481000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2480000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2384000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2539000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2780000</v>
       </c>
       <c r="I61" s="3">
         <v>2780000</v>
       </c>
       <c r="J61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="K61" s="3">
         <v>2779000</v>
       </c>
       <c r="L61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="M61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2777000</v>
       </c>
       <c r="N61" s="3">
         <v>2777000</v>
       </c>
       <c r="O61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="P61" s="3">
         <v>2776000</v>
       </c>
       <c r="Q61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="R61" s="3">
         <v>2680000</v>
       </c>
       <c r="S61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="T61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>2678000</v>
       </c>
       <c r="U61" s="3">
         <v>2678000</v>
       </c>
       <c r="V61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="W61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>2680000</v>
       </c>
       <c r="X61" s="3">
         <v>2680000</v>
       </c>
       <c r="Y61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="Z61" s="3">
         <v>2679000</v>
       </c>
       <c r="AA61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54818000</v>
+      </c>
+      <c r="E66" s="3">
         <v>53389000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54362000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53388000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52452000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52121000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52717000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52975000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53830000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53858000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53539000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51624000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51319000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>50754000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>50450000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>48043000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48397000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48327000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>47876000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47022000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>45935000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>45749000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>46443000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9755000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9503000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9359000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9191000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9336000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9433000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9415000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9319000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9663000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9500000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9348000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9084000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9081000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8796000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8683000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8634000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9348000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9171000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9159000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8976000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9277000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9456000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9216000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9893000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8563000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8726000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8667000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8548000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8094000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9512000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10817000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12809000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12664000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12668000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12089000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12707000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12021000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11645000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10362000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12215000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12123000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12087000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11455000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11217000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11510000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11415000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E81" s="3">
         <v>258000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>283000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>297000</v>
       </c>
-      <c r="G81" s="3">
-        <v>248000</v>
-      </c>
       <c r="H81" s="3">
+        <v>239000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-42000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>190000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>295000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>266000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>256000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>368000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>312000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>387000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>213000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>151000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-61000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>273000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>107000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>278000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>342000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-84000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>336000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>270000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>291000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>223000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>144000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>272000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>260000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>241000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,55 +7002,56 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16000</v>
+        <v>29000</v>
       </c>
       <c r="E83" s="3">
         <v>16000</v>
       </c>
       <c r="F83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G83" s="3">
         <v>12000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>13000</v>
       </c>
       <c r="H83" s="3">
         <v>13000</v>
       </c>
       <c r="I83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J83" s="3">
         <v>12000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>13000</v>
       </c>
       <c r="K83" s="3">
         <v>13000</v>
       </c>
       <c r="L83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="M83" s="3">
         <v>14000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>14000</v>
       </c>
       <c r="O83" s="3">
         <v>14000</v>
       </c>
       <c r="P83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="Q83" s="3">
         <v>15000</v>
       </c>
       <c r="R83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="S83" s="3">
         <v>16000</v>
@@ -6862,43 +7060,46 @@
         <v>16000</v>
       </c>
       <c r="U83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="V83" s="3">
         <v>17000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>19000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>21000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>22000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>23000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>22000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>21000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>520000</v>
+      </c>
+      <c r="E89" s="3">
         <v>828000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>501000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>436000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>512000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>737000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>608000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>645000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>643000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>669000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>603000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>82000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>367000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>758000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>438000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>212000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>160000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>466000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>227000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>287000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>359000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>514000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>136000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>218000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>360000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>379000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>233000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>282000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>296000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,58 +7702,59 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-6000</v>
       </c>
       <c r="T91" s="3">
         <v>-6000</v>
@@ -7543,40 +7763,43 @@
         <v>-6000</v>
       </c>
       <c r="V91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-8000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-38000</v>
       </c>
       <c r="Z91" s="3">
         <v>-38000</v>
       </c>
       <c r="AA91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-306000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-679000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-909000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>51000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-440000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-641000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-302000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-129000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-631000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-395000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-610000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>408000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-298000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-882000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-612000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1087000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-165000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-293000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-56000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>289000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-257000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-359000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>489000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>354000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7897,88 +8130,91 @@
         <v>-114000</v>
       </c>
       <c r="F96" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-445000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-108000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-109000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-108000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-657000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-104000</v>
       </c>
       <c r="M96" s="3">
         <v>-104000</v>
       </c>
       <c r="N96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-100000</v>
       </c>
       <c r="P96" s="3">
         <v>-100000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-101000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-649000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-95000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-96000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-95000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-95000</v>
       </c>
       <c r="X96" s="3">
         <v>-95000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-359000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>280000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-480000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-108000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-138000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-98000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-688000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-103000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-104000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-120000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-321000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-101000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-101000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-675000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-101000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-99000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-123000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-665000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-96000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-134000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-74000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-15000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>9000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AC101" s="3">
         <v>4000</v>
       </c>
       <c r="AD101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="E102" s="3">
         <v>127000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-125000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-57000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>199000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-175000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-89000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>163000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-126000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>169000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-23000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-144000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-271000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>615000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-98000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>69000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>48000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-87000</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>22000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>72000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>58000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>28000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3444000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3507000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3336000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3304000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3152000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3111000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2957000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2926000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2885000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3054000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2959000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3029000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2866000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2931000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2820000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2766000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2291000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2787000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2699000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2616000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2709000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2415000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2625000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>444000</v>
+      </c>
+      <c r="E9" s="3">
         <v>436000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>426000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>403000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>379000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>389000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>383000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>374000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>344000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>359000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>368000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>357000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>359000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>364000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>360000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>342000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>344000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>358000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>345000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>338000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>342000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>343000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>337000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>359000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>296000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>307000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>309000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>312000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>305000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>309000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3071000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2910000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2901000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2773000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2722000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2574000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2552000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2541000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2695000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2591000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2672000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2507000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2567000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2460000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2424000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1947000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2429000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2354000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2278000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2367000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2072000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2288000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1336,8 +1356,8 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1354,50 +1374,53 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>14000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>5000</v>
       </c>
       <c r="AC14" s="3">
         <v>5000</v>
       </c>
       <c r="AD14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AE14" s="3">
         <v>2000</v>
       </c>
       <c r="AF14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>25000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2982000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3013000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2976000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2912000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2753000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2800000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2980000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2671000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2502000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2696000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2617000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2538000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2460000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2425000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2538000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2553000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2349000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2421000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2540000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2240000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2256000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2495000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2189000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E18" s="3">
         <v>494000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>360000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>392000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>399000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>311000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-23000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>255000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>383000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>358000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>342000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>491000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>406000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>506000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>282000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>213000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-58000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>366000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>159000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>376000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>453000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-80000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>436000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>365000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>381000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>447000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>228000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>410000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>386000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>357000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1843,117 +1877,123 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>478000</v>
+      </c>
+      <c r="E21" s="3">
         <v>523000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>376000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>408000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>411000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>324000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>267000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>396000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>371000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>356000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>504000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>420000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>520000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>297000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>228000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-42000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>382000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>175000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>393000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>472000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>454000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>386000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>401000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>469000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>251000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>432000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>407000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>377000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>34000</v>
+        <v>35000</v>
       </c>
       <c r="E22" s="3">
         <v>34000</v>
       </c>
       <c r="F22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="G22" s="3">
         <v>31000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>28000</v>
       </c>
       <c r="H22" s="3">
         <v>28000</v>
@@ -1974,19 +2014,19 @@
         <v>28000</v>
       </c>
       <c r="N22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="O22" s="3">
         <v>29000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>28000</v>
       </c>
       <c r="P22" s="3">
         <v>28000</v>
       </c>
       <c r="Q22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="R22" s="3">
         <v>32000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>31000</v>
       </c>
       <c r="S22" s="3">
         <v>31000</v>
@@ -1995,10 +2035,10 @@
         <v>31000</v>
       </c>
       <c r="U22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="V22" s="3">
         <v>32000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>34000</v>
       </c>
       <c r="W22" s="3">
         <v>34000</v>
@@ -2010,221 +2050,230 @@
         <v>34000</v>
       </c>
       <c r="Z22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AA22" s="3">
         <v>35000</v>
       </c>
       <c r="AB22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>37000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>41000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>40000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>43000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>40000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>427000</v>
+      </c>
+      <c r="E23" s="3">
         <v>460000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>326000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>361000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>371000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>283000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-51000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>227000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>355000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>330000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>314000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>462000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>378000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>478000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>250000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>182000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-89000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>335000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>127000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>342000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>419000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-114000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>402000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>330000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>346000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>410000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>187000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>370000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>343000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>317000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E24" s="3">
         <v>93000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>68000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>74000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>44000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-9000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>37000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>60000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>64000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>58000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>94000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>66000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>91000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>31000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-28000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>62000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>20000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>64000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>77000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>66000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>60000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>55000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>104000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>43000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>98000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>83000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>76000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E26" s="3">
         <v>367000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>258000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>283000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>297000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>239000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-42000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>190000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>295000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>266000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>256000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>368000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>312000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>387000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>213000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>151000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-61000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>273000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>107000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>278000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>342000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>336000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>270000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>291000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>306000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>144000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>272000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>260000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>241000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E27" s="3">
         <v>367000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>258000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>283000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>297000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>239000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-42000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>190000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>295000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>266000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>256000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>368000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>312000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>387000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>213000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>151000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-61000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>273000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>107000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>278000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>342000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>336000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>270000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>291000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>306000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>144000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>272000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>260000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>241000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2662,8 +2723,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2680,11 +2741,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2692,14 +2753,17 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2983,103 +3053,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E33" s="3">
         <v>367000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>258000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>283000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>297000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>239000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-42000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>190000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>295000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>266000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>256000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>368000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>312000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>387000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>213000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>151000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-61000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>273000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>107000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>278000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>342000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>336000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>270000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>291000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>223000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>144000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>272000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>260000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>241000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E35" s="3">
         <v>367000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>258000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>283000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>297000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>239000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-42000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>190000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>295000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>266000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>256000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>368000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>312000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>387000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>213000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>151000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-61000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>273000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>107000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>278000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>342000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>336000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>270000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>291000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>223000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>144000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>272000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>260000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>241000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E41" s="3">
         <v>345000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>485000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>358000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>483000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>475000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>503000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>560000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>361000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>536000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>625000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>462000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>588000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>419000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>442000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>586000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>857000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>242000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>340000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>271000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>223000</v>
-      </c>
-      <c r="X41" s="3">
-        <v>310000</v>
       </c>
       <c r="Y41" s="3">
         <v>310000</v>
       </c>
       <c r="Z41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AA41" s="3">
         <v>288000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>282000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>355000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>283000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>225000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>299000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>271000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,103 +3718,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3432000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3442000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3211000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3521000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3126000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3158000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2986000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3210000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2892000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2945000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2799000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2954000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2652000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2607000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2527000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2755000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2502000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2481000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2504000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2690000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2476000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2365000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3913,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,198 +4110,207 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46674000</v>
+      </c>
+      <c r="E47" s="3">
         <v>46562000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>43647000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>44435000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44023000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43177000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>42137000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44280000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47106000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>50328000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50236000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50265000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>48671000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50293000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>49006000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>47757000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44086000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>47744000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>47535000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>46747000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>45639000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>44486000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>44929000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E48" s="3">
         <v>253000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>257000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>246000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>232000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>226000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>229000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>227000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>225000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>226000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>234000</v>
       </c>
       <c r="N48" s="3">
         <v>234000</v>
       </c>
       <c r="O48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="P48" s="3">
         <v>244000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>451000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>256000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>264000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>271000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>502000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>516000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>525000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>547000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>324000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>332000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>347000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>346000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>326000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>325000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>336000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>324000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>310000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4207,28 +4318,28 @@
         <v>146000</v>
       </c>
       <c r="E49" s="3">
+        <v>146000</v>
+      </c>
+      <c r="F49" s="3">
         <v>145000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>146000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>145000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>144000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>142000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>145000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>147000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>148000</v>
       </c>
       <c r="M49" s="3">
         <v>148000</v>
@@ -4243,58 +4354,61 @@
         <v>148000</v>
       </c>
       <c r="Q49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="R49" s="3">
         <v>146000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>145000</v>
       </c>
       <c r="S49" s="3">
         <v>145000</v>
       </c>
       <c r="T49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="U49" s="3">
         <v>147000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>145000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>146000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>147000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>146000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>147000</v>
       </c>
       <c r="Z49" s="3">
         <v>147000</v>
       </c>
       <c r="AA49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>149000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>147000</v>
       </c>
       <c r="AD49" s="3">
         <v>147000</v>
       </c>
       <c r="AE49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>146000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>145000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>942000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1016000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1277000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1201000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1157000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1251000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1298000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>927000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>547000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>142000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>135000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>121000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>197000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>144000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>195000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>518000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>199000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>190000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>106000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>217000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>392000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>314000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>296000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>238000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>137000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>141000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>166000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>267000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>379000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>65075000</v>
+      </c>
+      <c r="E54" s="3">
         <v>64711000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>61952000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>63088000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62055000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>61000000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>60215000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62229000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>63792000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66639000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66522000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>66207000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>63713000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>64026000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62775000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>62095000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58405000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>60612000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>60450000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59963000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58477000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>57152000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>57259000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4933,8 +5064,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4942,19 +5076,19 @@
         <v>550000</v>
       </c>
       <c r="E58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="F58" s="3">
         <v>793000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>792000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>243000</v>
       </c>
       <c r="H58" s="3">
         <v>243000</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
+      <c r="I58" s="3">
+        <v>243000</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
@@ -4971,8 +5105,8 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5005,13 +5139,13 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>30000</v>
       </c>
       <c r="AB58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AC58" s="3">
         <v>150000</v>
@@ -5023,108 +5157,114 @@
         <v>150000</v>
       </c>
       <c r="AF58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20559000</v>
+      </c>
+      <c r="E59" s="3">
         <v>20892000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19443000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20644000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20557000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19854000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16649000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17215000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17880000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19245000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18775000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18877000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18091000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18716000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17998000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17592000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16479000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17195000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17217000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16486000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15808000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14780000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14894000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,103 +5358,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2970000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2481000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2480000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2384000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2539000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2780000</v>
       </c>
       <c r="J61" s="3">
         <v>2780000</v>
       </c>
       <c r="K61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="L61" s="3">
         <v>2779000</v>
       </c>
       <c r="M61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="N61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2777000</v>
       </c>
       <c r="O61" s="3">
         <v>2777000</v>
       </c>
       <c r="P61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="Q61" s="3">
         <v>2776000</v>
       </c>
       <c r="R61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="S61" s="3">
         <v>2680000</v>
       </c>
       <c r="T61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="U61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>2678000</v>
       </c>
       <c r="V61" s="3">
         <v>2678000</v>
       </c>
       <c r="W61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="X61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>2680000</v>
       </c>
       <c r="Y61" s="3">
         <v>2680000</v>
       </c>
       <c r="Z61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AA61" s="3">
         <v>2679000</v>
       </c>
       <c r="AB61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55413000</v>
+      </c>
+      <c r="E66" s="3">
         <v>54818000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53389000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>54362000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53388000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52452000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52121000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52717000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52975000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53830000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53858000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53539000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51624000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51319000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>50754000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>50450000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48043000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48397000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48327000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47876000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>47022000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>45935000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45749000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9425000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9755000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9503000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9359000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9191000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9336000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9433000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9415000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9319000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9663000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9500000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9348000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9084000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9081000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8796000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8683000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8634000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9348000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9171000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9159000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8976000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9277000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9456000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9662000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9893000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8563000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8726000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8667000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8548000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8094000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9512000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10817000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12809000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12664000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12668000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12089000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12707000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12021000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11645000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10362000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12215000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12123000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12087000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11455000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11217000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11510000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E81" s="3">
         <v>367000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>258000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>283000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>297000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>239000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-42000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>190000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>295000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>266000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>256000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>368000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>312000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>387000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>213000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>151000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-61000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>273000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>107000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>278000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>342000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>336000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>270000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>291000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>223000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>144000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>272000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>260000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>241000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,58 +7201,59 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E83" s="3">
         <v>29000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>16000</v>
       </c>
       <c r="F83" s="3">
         <v>16000</v>
       </c>
       <c r="G83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H83" s="3">
         <v>12000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>13000</v>
       </c>
       <c r="I83" s="3">
         <v>13000</v>
       </c>
       <c r="J83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K83" s="3">
         <v>12000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>13000</v>
       </c>
       <c r="L83" s="3">
         <v>13000</v>
       </c>
       <c r="M83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N83" s="3">
         <v>14000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>14000</v>
       </c>
       <c r="P83" s="3">
         <v>14000</v>
       </c>
       <c r="Q83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="R83" s="3">
         <v>15000</v>
       </c>
       <c r="S83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="T83" s="3">
         <v>16000</v>
@@ -7063,43 +7262,46 @@
         <v>16000</v>
       </c>
       <c r="V83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="W83" s="3">
         <v>17000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>18000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>21000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>23000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>504000</v>
+      </c>
+      <c r="E89" s="3">
         <v>520000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>828000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>501000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>436000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>512000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>737000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>608000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>645000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>643000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>669000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>603000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>82000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>367000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>758000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>438000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>212000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>160000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>466000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>227000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>287000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>359000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>514000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>136000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>218000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>360000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>379000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>233000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>282000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>296000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,61 +7923,62 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-6000</v>
       </c>
       <c r="U91" s="3">
         <v>-6000</v>
@@ -7766,40 +7987,43 @@
         <v>-6000</v>
       </c>
       <c r="W91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-8000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AA91" s="3">
         <v>-38000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-249000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-306000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-679000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-909000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>51000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-440000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-641000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-302000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-129000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-631000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-395000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-610000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>408000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-298000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-882000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-612000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1087000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-165000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-293000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-56000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>289000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-257000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-359000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>489000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>354000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,13 +8351,14 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-114000</v>
+        <v>-667000</v>
       </c>
       <c r="E96" s="3">
         <v>-114000</v>
@@ -8133,88 +8367,91 @@
         <v>-114000</v>
       </c>
       <c r="G96" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-445000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-108000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-109000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-108000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-657000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-104000</v>
       </c>
       <c r="N96" s="3">
         <v>-104000</v>
       </c>
       <c r="O96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-100000</v>
       </c>
       <c r="Q96" s="3">
         <v>-100000</v>
       </c>
       <c r="R96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-101000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-649000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-95000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-96000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-95000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-95000</v>
       </c>
       <c r="Y96" s="3">
         <v>-95000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-189000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-359000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>280000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-480000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-108000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-138000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-98000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-688000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-103000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-104000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-120000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-321000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-25000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-101000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-675000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-101000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-99000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-123000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-665000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-96000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-134000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-15000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>9000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AD101" s="3">
         <v>4000</v>
       </c>
       <c r="AE101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-140000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>127000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-125000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-57000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>199000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-175000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-89000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>163000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-126000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>169000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-144000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-271000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>615000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-98000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>69000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>48000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-87000</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>22000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>72000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>58000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>28000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3519000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3444000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3507000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3336000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3304000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3152000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3111000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2957000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2926000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2885000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3054000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2959000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3029000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2866000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2931000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2820000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2766000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2291000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2787000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2699000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2616000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2709000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2415000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2625000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E9" s="3">
         <v>444000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>436000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>426000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>403000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>379000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>389000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>383000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>374000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>344000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>359000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>368000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>357000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>359000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>364000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>360000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>342000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>344000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>358000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>345000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>338000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>342000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>343000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>337000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>359000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>296000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>307000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>309000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>312000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>305000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>309000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3084000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3000000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3071000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2910000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2901000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2773000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2722000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2574000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2552000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2541000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2695000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2591000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2672000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2507000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2567000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2460000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2424000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1947000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2429000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2354000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2278000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2367000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2072000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2288000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1359,8 +1379,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1377,50 +1397,53 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>10000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>5000</v>
       </c>
       <c r="AD14" s="3">
         <v>5000</v>
       </c>
       <c r="AE14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AF14" s="3">
         <v>2000</v>
       </c>
       <c r="AG14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH14" s="3">
         <v>25000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3083000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2982000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3013000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2976000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2912000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2753000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2800000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2980000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2671000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2502000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2696000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2617000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2538000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2460000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2425000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2538000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2553000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2349000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2421000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2540000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2240000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2256000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2495000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2189000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>436000</v>
+      </c>
+      <c r="E18" s="3">
         <v>462000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>494000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>360000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>392000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>399000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>311000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>255000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>383000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>358000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>342000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>491000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>406000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>506000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>282000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>213000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-58000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>366000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>159000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>376000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>453000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-80000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>436000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>365000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>381000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>447000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>228000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>410000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>386000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>357000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1880,123 +1914,129 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E21" s="3">
         <v>478000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>523000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>376000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>408000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>411000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>324000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>267000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>396000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>371000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>356000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>504000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>420000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>520000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>297000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>228000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-42000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>382000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>175000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>393000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>472000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>454000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>386000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>401000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>469000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>251000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>432000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>407000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>377000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E22" s="3">
         <v>35000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>34000</v>
       </c>
       <c r="F22" s="3">
         <v>34000</v>
       </c>
       <c r="G22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="H22" s="3">
         <v>31000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>28000</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
@@ -2017,19 +2057,19 @@
         <v>28000</v>
       </c>
       <c r="O22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="P22" s="3">
         <v>29000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>28000</v>
       </c>
       <c r="Q22" s="3">
         <v>28000</v>
       </c>
       <c r="R22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="S22" s="3">
         <v>32000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>31000</v>
       </c>
       <c r="T22" s="3">
         <v>31000</v>
@@ -2038,10 +2078,10 @@
         <v>31000</v>
       </c>
       <c r="V22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="W22" s="3">
         <v>32000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>34000</v>
       </c>
       <c r="X22" s="3">
         <v>34000</v>
@@ -2053,227 +2093,236 @@
         <v>34000</v>
       </c>
       <c r="AA22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AB22" s="3">
         <v>35000</v>
       </c>
       <c r="AC22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>37000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>41000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>40000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>43000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>40000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>402000</v>
+      </c>
+      <c r="E23" s="3">
         <v>427000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>460000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>326000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>361000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>371000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>283000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>227000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>355000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>330000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>314000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>462000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>378000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>478000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>250000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>182000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-89000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>335000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>127000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>342000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>419000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-114000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>402000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>330000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>346000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>410000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>187000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>370000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>343000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>317000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E24" s="3">
         <v>89000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>93000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>68000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>78000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>74000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>44000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-9000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>37000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>60000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>58000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>94000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>66000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>91000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>31000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-28000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>62000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>20000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>64000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>77000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>66000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>60000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>55000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>104000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>43000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>98000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>83000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>76000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>317000</v>
+      </c>
+      <c r="E26" s="3">
         <v>338000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>367000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>258000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>283000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>297000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>239000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>190000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>295000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>266000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>256000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>368000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>312000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>387000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>213000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>151000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-61000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>273000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>107000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>278000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>342000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>336000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>270000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>291000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>306000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>144000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>272000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>260000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>241000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>317000</v>
+      </c>
+      <c r="E27" s="3">
         <v>338000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>367000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>258000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>283000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>297000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>239000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>190000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>295000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>266000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>256000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>368000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>312000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>387000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>213000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>151000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-61000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>273000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>107000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>278000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>342000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>336000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>270000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>291000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>306000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>144000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>272000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>260000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>241000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,8 +2787,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2744,11 +2805,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2756,14 +2817,17 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>317000</v>
+      </c>
+      <c r="E33" s="3">
         <v>338000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>367000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>258000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>283000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>297000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>239000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-42000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>190000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>295000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>266000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>256000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>368000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>312000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>387000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>213000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>151000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-61000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>273000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>107000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>278000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>342000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>336000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>270000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>291000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>223000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>144000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>272000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>260000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>241000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>317000</v>
+      </c>
+      <c r="E35" s="3">
         <v>338000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>367000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>258000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>283000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>297000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>239000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-42000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>190000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>295000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>266000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>256000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>368000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>312000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>387000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>213000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>151000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-61000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>273000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>107000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>278000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>342000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>336000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>270000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>291000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>223000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>144000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>272000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>260000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>241000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E41" s="3">
         <v>409000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>345000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>485000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>358000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>483000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>475000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>503000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>560000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>361000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>536000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>625000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>462000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>588000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>419000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>442000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>586000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>857000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>242000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>340000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>271000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>223000</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>310000</v>
       </c>
       <c r="Z41" s="3">
         <v>310000</v>
       </c>
       <c r="AA41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AB41" s="3">
         <v>288000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>282000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>355000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>283000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>225000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>299000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>271000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3816000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3432000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3442000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3211000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3521000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3126000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3158000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2986000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3210000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2892000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2945000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2799000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2954000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2652000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2607000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2527000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2755000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2502000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2481000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2504000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2690000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2476000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2365000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2400000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,204 +4215,213 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46245000</v>
+      </c>
+      <c r="E47" s="3">
         <v>46674000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46562000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43647000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44435000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>44023000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43177000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>42137000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44280000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>47106000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50328000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50236000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50265000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>48671000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50293000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>49006000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>47757000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>44086000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>47744000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>47535000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>46747000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>45639000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>44486000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>44929000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E48" s="3">
         <v>256000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>253000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>257000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>246000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>232000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>226000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>229000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>227000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>225000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>226000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>234000</v>
       </c>
       <c r="O48" s="3">
         <v>234000</v>
       </c>
       <c r="P48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>244000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>451000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>256000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>264000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>271000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>502000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>516000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>525000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>547000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>324000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>332000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>347000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>346000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>326000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>325000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>336000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>324000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>310000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4321,28 +4432,28 @@
         <v>146000</v>
       </c>
       <c r="F49" s="3">
+        <v>146000</v>
+      </c>
+      <c r="G49" s="3">
         <v>145000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>146000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>145000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>144000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>142000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>145000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>147000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>148000</v>
       </c>
       <c r="N49" s="3">
         <v>148000</v>
@@ -4357,58 +4468,61 @@
         <v>148000</v>
       </c>
       <c r="R49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="S49" s="3">
         <v>146000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>145000</v>
       </c>
       <c r="T49" s="3">
         <v>145000</v>
       </c>
       <c r="U49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="V49" s="3">
         <v>147000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>145000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>146000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>147000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>146000</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>147000</v>
       </c>
       <c r="AA49" s="3">
         <v>147000</v>
       </c>
       <c r="AB49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>149000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>147000</v>
       </c>
       <c r="AE49" s="3">
         <v>147000</v>
       </c>
       <c r="AF49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>146000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>145000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>941000</v>
+      </c>
+      <c r="E52" s="3">
         <v>942000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1016000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1277000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1201000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1157000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1251000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1298000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>927000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>547000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>142000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>135000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>121000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>197000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>66000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>144000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>195000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>518000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>199000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>190000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>106000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>217000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>392000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>314000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>296000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>238000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>137000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>141000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>166000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>267000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>379000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>65194000</v>
+      </c>
+      <c r="E54" s="3">
         <v>65075000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>64711000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>61952000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>63088000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>62055000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>61000000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>60215000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62229000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>63792000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66639000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>66522000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66207000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>63713000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>64026000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>62775000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62095000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58405000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>60612000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>60450000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59963000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58477000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>57152000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>57259000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5067,31 +5198,34 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>550000</v>
       </c>
       <c r="F58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="G58" s="3">
         <v>793000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>792000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>243000</v>
       </c>
       <c r="I58" s="3">
         <v>243000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+      <c r="J58" s="3">
+        <v>243000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -5108,8 +5242,8 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -5142,13 +5276,13 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>30000</v>
       </c>
       <c r="AC58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AD58" s="3">
         <v>150000</v>
@@ -5160,111 +5294,117 @@
         <v>150000</v>
       </c>
       <c r="AG58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20620000</v>
+      </c>
+      <c r="E59" s="3">
         <v>20559000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20892000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19443000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20644000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20557000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19854000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16649000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17215000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17880000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19245000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18775000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18877000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18091000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18716000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17998000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17592000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16479000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17195000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17217000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16486000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15808000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14780000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14894000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,106 +5501,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2971000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2970000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2481000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2480000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2384000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2539000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2780000</v>
       </c>
       <c r="K61" s="3">
         <v>2780000</v>
       </c>
       <c r="L61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="M61" s="3">
         <v>2779000</v>
       </c>
       <c r="N61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="O61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2777000</v>
       </c>
       <c r="P61" s="3">
         <v>2777000</v>
       </c>
       <c r="Q61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="R61" s="3">
         <v>2776000</v>
       </c>
       <c r="S61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="T61" s="3">
         <v>2680000</v>
       </c>
       <c r="U61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="V61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>2678000</v>
       </c>
       <c r="W61" s="3">
         <v>2678000</v>
       </c>
       <c r="X61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>2680000</v>
       </c>
       <c r="Z61" s="3">
         <v>2680000</v>
       </c>
       <c r="AA61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AB61" s="3">
         <v>2679000</v>
       </c>
       <c r="AC61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55320000</v>
+      </c>
+      <c r="E66" s="3">
         <v>55413000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54818000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53389000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54362000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53388000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52452000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52121000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52717000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52975000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53830000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53858000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53539000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51624000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51319000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>50754000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>50450000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48043000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48397000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>48327000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>47876000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47022000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45935000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45749000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9623000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9425000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9755000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9503000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9359000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9191000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9336000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9433000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9415000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9319000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9663000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9500000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9348000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9084000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9081000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8796000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8683000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8634000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9348000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9171000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9159000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8976000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9277000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9456000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9874000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9662000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9893000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8563000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8726000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8667000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8548000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8094000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9512000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10817000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12809000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12664000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12668000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12089000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12707000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12021000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11645000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10362000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12215000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12123000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12087000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11455000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11217000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11510000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>317000</v>
+      </c>
+      <c r="E81" s="3">
         <v>338000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>367000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>258000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>283000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>297000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>239000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-42000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>190000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>295000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>266000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>256000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>368000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>312000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>387000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>213000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>151000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-61000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>273000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>107000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>278000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>342000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>336000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>270000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>291000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>223000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>144000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>272000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>260000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>241000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,61 +7400,62 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E83" s="3">
         <v>16000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>29000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>16000</v>
       </c>
       <c r="G83" s="3">
         <v>16000</v>
       </c>
       <c r="H83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I83" s="3">
         <v>12000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>13000</v>
       </c>
       <c r="J83" s="3">
         <v>13000</v>
       </c>
       <c r="K83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L83" s="3">
         <v>12000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>13000</v>
       </c>
       <c r="M83" s="3">
         <v>13000</v>
       </c>
       <c r="N83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O83" s="3">
         <v>14000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>14000</v>
       </c>
       <c r="Q83" s="3">
         <v>14000</v>
       </c>
       <c r="R83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="S83" s="3">
         <v>15000</v>
       </c>
       <c r="T83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="U83" s="3">
         <v>16000</v>
@@ -7265,43 +7464,46 @@
         <v>16000</v>
       </c>
       <c r="W83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="X83" s="3">
         <v>17000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>19000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>18000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>21000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>22000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>23000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>22000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>20000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>616000</v>
+      </c>
+      <c r="E89" s="3">
         <v>504000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>520000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>828000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>501000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>436000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>512000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>737000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>608000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>645000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>643000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>669000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>603000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>82000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>367000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>758000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>438000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>212000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>160000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>466000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>227000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>287000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>359000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>514000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>136000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>218000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>360000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>379000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>233000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>282000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>296000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,64 +8144,65 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-6000</v>
       </c>
       <c r="V91" s="3">
         <v>-6000</v>
@@ -7990,40 +8211,43 @@
         <v>-6000</v>
       </c>
       <c r="X91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AB91" s="3">
         <v>-38000</v>
       </c>
       <c r="AC91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-249000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-306000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-679000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-909000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>51000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-440000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-641000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-302000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-129000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-631000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-395000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-610000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>408000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-298000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-882000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-612000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1087000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-165000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-293000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-56000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>289000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-257000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>489000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>354000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,16 +8585,17 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-667000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-114000</v>
       </c>
       <c r="F96" s="3">
         <v>-114000</v>
@@ -8370,88 +8604,91 @@
         <v>-114000</v>
       </c>
       <c r="H96" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-445000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-108000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-109000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-108000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-657000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-104000</v>
       </c>
       <c r="O96" s="3">
         <v>-104000</v>
       </c>
       <c r="P96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-100000</v>
       </c>
       <c r="R96" s="3">
         <v>-100000</v>
       </c>
       <c r="S96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-101000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-649000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-95000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-96000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-95000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-95000</v>
       </c>
       <c r="Z96" s="3">
         <v>-95000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-689000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-189000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-359000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>280000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-480000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-108000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-138000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-98000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-688000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-103000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-104000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-120000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-321000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-101000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-101000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-675000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-101000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-99000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-123000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-665000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-96000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-134000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-15000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>9000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-9000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AE101" s="3">
         <v>4000</v>
       </c>
       <c r="AF101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E102" s="3">
         <v>64000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-140000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>127000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-125000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-57000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>199000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-175000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-89000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>163000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-126000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>169000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-23000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-144000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-271000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>615000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-98000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>69000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>48000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-87000</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>22000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>72000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>58000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>28000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3618000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3519000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3444000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3507000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3336000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3304000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3152000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3111000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2957000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2926000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2885000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3054000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2959000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3029000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2866000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2931000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2820000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2766000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2291000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2787000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2699000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2616000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2709000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2625000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>435000</v>
+        <v>2476000</v>
       </c>
       <c r="E9" s="3">
-        <v>444000</v>
+        <v>2317000</v>
       </c>
       <c r="F9" s="3">
-        <v>436000</v>
+        <v>2251000</v>
       </c>
       <c r="G9" s="3">
-        <v>426000</v>
+        <v>2246000</v>
       </c>
       <c r="H9" s="3">
-        <v>403000</v>
+        <v>2252000</v>
       </c>
       <c r="I9" s="3">
-        <v>379000</v>
+        <v>2182000</v>
       </c>
       <c r="J9" s="3">
+        <v>2032000</v>
+      </c>
+      <c r="K9" s="3">
         <v>389000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>383000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>374000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>344000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>359000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>368000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>357000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>359000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>364000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>360000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>342000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>344000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>358000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>345000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>338000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>342000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>343000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>337000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>359000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>296000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>307000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>309000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>312000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>305000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>309000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3084000</v>
+        <v>1142000</v>
       </c>
       <c r="E10" s="3">
-        <v>3000000</v>
+        <v>1202000</v>
       </c>
       <c r="F10" s="3">
-        <v>3071000</v>
+        <v>1193000</v>
       </c>
       <c r="G10" s="3">
-        <v>2910000</v>
+        <v>1261000</v>
       </c>
       <c r="H10" s="3">
-        <v>2901000</v>
+        <v>1084000</v>
       </c>
       <c r="I10" s="3">
-        <v>2773000</v>
+        <v>1122000</v>
       </c>
       <c r="J10" s="3">
+        <v>1120000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2722000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2574000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2552000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2541000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2695000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2591000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2672000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2507000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2567000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2460000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2424000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1947000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2429000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2354000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2278000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2367000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2288000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1382,8 +1402,8 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1400,73 +1420,76 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>10000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>5000</v>
       </c>
       <c r="AE14" s="3">
         <v>5000</v>
       </c>
       <c r="AF14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AG14" s="3">
         <v>2000</v>
       </c>
       <c r="AH14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AI14" s="3">
         <v>25000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3225000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3083000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2982000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3013000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2976000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2912000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2753000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2800000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2980000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2671000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2502000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2696000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2617000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2538000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2460000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2425000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2538000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2553000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2349000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2421000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2540000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2240000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2256000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2189000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E18" s="3">
         <v>436000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>462000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>494000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>360000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>392000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>399000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>311000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>255000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>383000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>358000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>342000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>491000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>406000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>506000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>282000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>213000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-58000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>366000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>159000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>376000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>453000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-80000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>436000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>365000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>381000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>447000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>228000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>410000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>386000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>357000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,31 +1849,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1917,129 +1951,135 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E21" s="3">
         <v>454000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>478000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>523000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>376000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>408000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>411000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>324000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>267000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>396000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>371000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>356000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>504000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>420000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>520000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>297000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>228000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-42000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>382000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>175000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>393000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>472000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>454000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>386000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>401000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>469000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>251000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>432000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>407000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>377000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E22" s="3">
         <v>34000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>34000</v>
       </c>
       <c r="G22" s="3">
         <v>34000</v>
       </c>
       <c r="H22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I22" s="3">
         <v>31000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>28000</v>
       </c>
       <c r="J22" s="3">
         <v>28000</v>
@@ -2060,19 +2100,19 @@
         <v>28000</v>
       </c>
       <c r="P22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>29000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>28000</v>
       </c>
       <c r="R22" s="3">
         <v>28000</v>
       </c>
       <c r="S22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="T22" s="3">
         <v>32000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>31000</v>
       </c>
       <c r="U22" s="3">
         <v>31000</v>
@@ -2081,10 +2121,10 @@
         <v>31000</v>
       </c>
       <c r="W22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="X22" s="3">
         <v>32000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>34000</v>
       </c>
       <c r="Y22" s="3">
         <v>34000</v>
@@ -2096,233 +2136,242 @@
         <v>34000</v>
       </c>
       <c r="AB22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AC22" s="3">
         <v>35000</v>
       </c>
       <c r="AD22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>37000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>41000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>40000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>43000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>40000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E23" s="3">
         <v>402000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>427000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>460000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>326000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>361000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>371000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>283000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-51000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>227000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>355000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>330000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>314000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>462000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>378000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>478000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>250000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>182000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-89000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>335000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>127000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>342000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>419000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-114000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>402000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>330000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>346000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>410000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>187000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>370000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>343000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>317000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E24" s="3">
         <v>85000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>89000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>93000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>68000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>78000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>74000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>44000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-9000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>37000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>60000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>58000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>94000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>66000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>91000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>31000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-28000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>62000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>20000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>64000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>77000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>66000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>60000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>55000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>104000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>43000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>98000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>83000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>76000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E26" s="3">
         <v>317000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>338000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>367000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>258000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>283000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>297000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>239000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-42000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>190000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>295000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>266000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>256000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>368000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>312000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>387000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>213000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>151000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-61000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>273000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>107000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>278000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>342000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>336000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>270000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>291000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>306000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>144000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>272000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>260000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>241000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E27" s="3">
         <v>317000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>338000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>367000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>258000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>283000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>297000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>239000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-42000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>190000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>295000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>266000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>256000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>368000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>312000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>387000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>213000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>151000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-61000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>273000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>107000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>278000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>342000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>336000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>270000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>291000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>306000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>144000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>272000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>260000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>241000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,8 +2851,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2808,11 +2869,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2820,14 +2881,17 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,31 +3095,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3129,109 +3199,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E33" s="3">
         <v>317000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>338000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>367000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>258000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>283000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>297000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>239000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-42000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>190000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>295000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>266000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>256000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>368000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>312000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>387000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>213000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>151000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-61000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>273000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>107000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>278000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>342000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>336000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>270000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>291000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>223000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>144000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>272000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>260000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>241000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E35" s="3">
         <v>317000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>338000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>367000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>258000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>283000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>297000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>239000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-42000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>190000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>295000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>266000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>256000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>368000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>312000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>387000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>213000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>151000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-61000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>273000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>107000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>278000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>342000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>336000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>270000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>291000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>223000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>144000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>272000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>260000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>241000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,132 +3698,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E41" s="3">
         <v>375000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>409000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>345000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>485000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>358000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>483000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>475000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>503000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>560000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>361000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>536000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>625000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>462000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>588000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>419000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>442000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>586000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>857000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>242000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>340000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>271000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>223000</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>310000</v>
       </c>
       <c r="AA41" s="3">
         <v>310000</v>
       </c>
       <c r="AB41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AC41" s="3">
         <v>288000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>282000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>355000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>283000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>225000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>299000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>271000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1900000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1747000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1996000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>2165000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1961000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1924000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1181000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3814,132 +3904,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3494000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3816000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3432000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3442000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3211000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3521000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3126000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3158000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2986000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3210000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2892000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2945000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2799000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2954000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2652000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2607000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2527000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2755000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2502000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2481000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2504000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2690000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2476000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2365000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2400000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4112,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>6258000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>6105000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>6021000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>5856000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>5888000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>6005000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>5899000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4117,31 +4216,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>12108000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>12043000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>11858000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>11808000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>11545000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>11808000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>10689000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,245 +4320,254 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>46245000</v>
+        <v>45792000</v>
       </c>
       <c r="E47" s="3">
-        <v>46674000</v>
+        <v>43512000</v>
       </c>
       <c r="F47" s="3">
-        <v>46562000</v>
+        <v>43649000</v>
       </c>
       <c r="G47" s="3">
-        <v>43647000</v>
+        <v>43362000</v>
       </c>
       <c r="H47" s="3">
-        <v>44435000</v>
+        <v>40691000</v>
       </c>
       <c r="I47" s="3">
-        <v>44023000</v>
+        <v>41502000</v>
       </c>
       <c r="J47" s="3">
+        <v>41836000</v>
+      </c>
+      <c r="K47" s="3">
         <v>43177000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>42137000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44280000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>47106000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50328000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50236000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50265000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>48671000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50293000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>49006000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>47757000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>44086000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>47744000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>47535000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>46747000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>45639000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>44486000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>44929000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>258000</v>
+      </c>
+      <c r="E48" s="3">
         <v>259000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>256000</v>
       </c>
-      <c r="F48" s="3">
-        <v>253000</v>
-      </c>
       <c r="G48" s="3">
+        <v>393000</v>
+      </c>
+      <c r="H48" s="3">
         <v>257000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>246000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>232000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>226000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>229000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>227000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>225000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>226000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>234000</v>
       </c>
       <c r="P48" s="3">
         <v>234000</v>
       </c>
       <c r="Q48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="R48" s="3">
         <v>244000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>451000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>256000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>264000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>271000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>502000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>516000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>525000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>547000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>324000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>332000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>347000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>346000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>326000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>325000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>336000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>324000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>310000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>146000</v>
+        <v>1090000</v>
       </c>
       <c r="E49" s="3">
-        <v>146000</v>
+        <v>1094000</v>
       </c>
       <c r="F49" s="3">
-        <v>146000</v>
+        <v>1073000</v>
       </c>
       <c r="G49" s="3">
+        <v>1120000</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1031000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>997000</v>
+      </c>
+      <c r="K49" s="3">
+        <v>144000</v>
+      </c>
+      <c r="L49" s="3">
+        <v>142000</v>
+      </c>
+      <c r="M49" s="3">
         <v>145000</v>
       </c>
-      <c r="H49" s="3">
-        <v>146000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>145000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>144000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>142000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>145000</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>147000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>148000</v>
       </c>
       <c r="O49" s="3">
         <v>148000</v>
@@ -4471,58 +4582,61 @@
         <v>148000</v>
       </c>
       <c r="S49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="T49" s="3">
         <v>146000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>145000</v>
       </c>
       <c r="U49" s="3">
         <v>145000</v>
       </c>
       <c r="V49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="W49" s="3">
         <v>147000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>145000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>146000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>147000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>146000</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>147000</v>
       </c>
       <c r="AB49" s="3">
         <v>147000</v>
       </c>
       <c r="AC49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>149000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>147000</v>
       </c>
       <c r="AF49" s="3">
         <v>147000</v>
       </c>
       <c r="AG49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>146000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>145000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>941000</v>
+        <v>2779000</v>
       </c>
       <c r="E52" s="3">
-        <v>942000</v>
+        <v>2761000</v>
       </c>
       <c r="F52" s="3">
-        <v>1016000</v>
+        <v>2647000</v>
       </c>
       <c r="G52" s="3">
-        <v>1277000</v>
+        <v>2316000</v>
       </c>
       <c r="H52" s="3">
-        <v>1201000</v>
+        <v>2474000</v>
       </c>
       <c r="I52" s="3">
-        <v>1157000</v>
+        <v>2602000</v>
       </c>
       <c r="J52" s="3">
+        <v>2467000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1251000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1298000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>927000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>547000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>142000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>135000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>121000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>197000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>66000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>144000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>195000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>518000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>199000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>190000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>106000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>217000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>392000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>314000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>296000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>238000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>137000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>141000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>166000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>267000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>379000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>67356000</v>
+      </c>
+      <c r="E54" s="3">
         <v>65194000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>65075000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>64711000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61952000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>63088000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>62055000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>61000000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>60215000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62229000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>63792000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>66639000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66522000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66207000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>63713000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>64026000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62775000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>62095000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58405000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>60612000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>60450000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>59963000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>58477000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>57152000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57259000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,31 +5230,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>24558000</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>23974000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>23588000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>23721000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>22836000</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>22802000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>22409000</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5201,8 +5332,11 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,25 +5344,25 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>550000</v>
       </c>
       <c r="G58" s="3">
+        <v>586000</v>
+      </c>
+      <c r="H58" s="3">
         <v>793000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>792000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>243000</v>
       </c>
       <c r="J58" s="3">
         <v>243000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
+      <c r="K58" s="3">
+        <v>243000</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
@@ -5245,8 +5379,8 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5279,13 +5413,13 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>30000</v>
       </c>
       <c r="AD58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AE58" s="3">
         <v>150000</v>
@@ -5297,137 +5431,143 @@
         <v>150000</v>
       </c>
       <c r="AH58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20620000</v>
+        <v>7659000</v>
       </c>
       <c r="E59" s="3">
-        <v>20559000</v>
+        <v>8209000</v>
       </c>
       <c r="F59" s="3">
-        <v>20892000</v>
+        <v>8146000</v>
       </c>
       <c r="G59" s="3">
-        <v>19443000</v>
+        <v>8334000</v>
       </c>
       <c r="H59" s="3">
-        <v>20644000</v>
+        <v>7689000</v>
       </c>
       <c r="I59" s="3">
-        <v>20557000</v>
+        <v>7878000</v>
       </c>
       <c r="J59" s="3">
+        <v>7781000</v>
+      </c>
+      <c r="K59" s="3">
         <v>19854000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16649000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17215000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17880000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19245000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18775000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18877000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18091000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18716000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17998000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17592000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16479000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17195000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17217000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16486000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15808000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14780000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14894000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>32217000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>32183000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>32284000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>32669000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>31318000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>31472000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>30433000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,132 +5644,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2972000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2971000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2970000</v>
       </c>
-      <c r="F61" s="3">
-        <v>2481000</v>
-      </c>
       <c r="G61" s="3">
+        <v>2660000</v>
+      </c>
+      <c r="H61" s="3">
         <v>2480000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2384000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2539000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2780000</v>
       </c>
       <c r="L61" s="3">
         <v>2780000</v>
       </c>
       <c r="M61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="N61" s="3">
         <v>2779000</v>
       </c>
       <c r="O61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="P61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2777000</v>
       </c>
       <c r="Q61" s="3">
         <v>2777000</v>
       </c>
       <c r="R61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="S61" s="3">
         <v>2776000</v>
       </c>
       <c r="T61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="U61" s="3">
         <v>2680000</v>
       </c>
       <c r="V61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="W61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>2678000</v>
       </c>
       <c r="X61" s="3">
         <v>2678000</v>
       </c>
       <c r="Y61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>2680000</v>
       </c>
       <c r="AA61" s="3">
         <v>2680000</v>
       </c>
       <c r="AB61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AC61" s="3">
         <v>2679000</v>
       </c>
       <c r="AD61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>17215000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>16343000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>16614000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>16144000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>15755000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>16671000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>16906000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>56598000</v>
+      </c>
+      <c r="E66" s="3">
         <v>55320000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55413000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>54818000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53389000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54362000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53388000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52452000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52121000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52717000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52975000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53830000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53858000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53539000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51624000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51319000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>50754000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>50450000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48043000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>48397000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48327000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47876000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47022000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45935000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>45749000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9785000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9623000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9425000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9755000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9503000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9359000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9191000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9336000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9433000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9415000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9319000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9663000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9500000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9348000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9084000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9081000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8796000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8683000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8634000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9348000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9171000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9159000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8976000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9277000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9456000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10758000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9874000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9662000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9893000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8563000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8726000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8667000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8548000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8094000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9512000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10817000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12809000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12664000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12668000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12089000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12707000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12021000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11645000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10362000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12215000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12123000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12087000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11455000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11217000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11510000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E81" s="3">
         <v>317000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>338000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>367000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>258000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>283000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>297000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>239000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-42000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>190000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>295000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>266000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>256000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>368000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>312000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>387000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>213000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>151000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-61000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>273000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>107000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>278000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>342000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>336000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>270000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>291000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>223000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>144000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>272000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>260000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>241000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,25 +7599,26 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="E83" s="3">
         <v>16000</v>
       </c>
       <c r="F83" s="3">
-        <v>29000</v>
+        <v>12000</v>
       </c>
       <c r="G83" s="3">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="H83" s="3">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="I83" s="3">
         <v>12000</v>
@@ -7431,34 +7630,34 @@
         <v>13000</v>
       </c>
       <c r="L83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="M83" s="3">
         <v>12000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>13000</v>
       </c>
       <c r="N83" s="3">
         <v>13000</v>
       </c>
       <c r="O83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="P83" s="3">
         <v>14000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>14000</v>
       </c>
       <c r="R83" s="3">
         <v>14000</v>
       </c>
       <c r="S83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="T83" s="3">
         <v>15000</v>
       </c>
       <c r="U83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="V83" s="3">
         <v>16000</v>
@@ -7467,43 +7666,46 @@
         <v>16000</v>
       </c>
       <c r="X83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>17000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>19000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>18000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>21000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>23000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>748000</v>
+      </c>
+      <c r="E89" s="3">
         <v>616000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>504000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>520000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>828000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>501000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>436000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>512000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>737000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>608000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>645000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>643000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>669000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>603000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>82000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>367000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>758000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>438000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>212000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>160000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>466000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>227000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>287000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>359000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>514000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>136000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>218000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>360000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>379000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>233000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>282000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>296000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,67 +8365,68 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-6000</v>
       </c>
       <c r="W91" s="3">
         <v>-6000</v>
@@ -8214,40 +8435,43 @@
         <v>-6000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AC91" s="3">
         <v>-38000</v>
       </c>
       <c r="AD91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-553000</v>
+      </c>
+      <c r="E94" s="3">
         <v>40000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-249000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-306000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-679000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-909000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>51000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-440000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-641000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-302000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-129000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-631000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-395000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-610000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>408000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-298000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-882000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-612000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1087000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-165000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-293000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>289000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-257000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>489000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>354000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-119000</v>
+        <v>120100</v>
       </c>
       <c r="E96" s="3">
-        <v>-667000</v>
+        <v>119900</v>
       </c>
       <c r="F96" s="3">
-        <v>-114000</v>
+        <v>120300</v>
       </c>
       <c r="G96" s="3">
-        <v>-114000</v>
+        <v>114400</v>
       </c>
       <c r="H96" s="3">
-        <v>-114000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-445000</v>
+        <v>442800</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J96" s="3">
+        <v>445000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-108000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-109000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-108000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-657000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-104000</v>
       </c>
       <c r="P96" s="3">
         <v>-104000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-100000</v>
       </c>
       <c r="S96" s="3">
         <v>-100000</v>
       </c>
       <c r="T96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-101000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-649000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-95000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-96000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-95000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AA96" s="3">
         <v>-95000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-120000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-689000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-189000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-359000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>280000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-480000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-108000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-138000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-98000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-688000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-103000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-104000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-321000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-101000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-25000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-101000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-675000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-101000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-99000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-123000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-665000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-96000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-134000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1000</v>
+        <v>-4000</v>
       </c>
       <c r="E101" s="3">
-        <v>-2000</v>
+        <v>3000</v>
       </c>
       <c r="F101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>9000</v>
+      </c>
+      <c r="T101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="U101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="AC101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>9000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>5000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>8000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AF101" s="3">
         <v>4000</v>
       </c>
       <c r="AG101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-34000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>64000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-140000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>127000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-125000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-57000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>199000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-175000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-89000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>163000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>169000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-23000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-144000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-271000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>615000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-98000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>69000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>48000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-87000</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>22000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>72000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>58000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>28000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3689000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3618000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3519000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3444000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3507000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3336000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3304000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3152000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3111000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2957000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2926000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2885000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3054000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2959000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3029000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2866000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2931000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2820000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2766000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2291000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2787000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2699000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2616000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2709000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2625000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2492000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2476000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2317000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2251000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2246000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2252000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2182000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2032000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>389000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>383000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>374000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>344000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>359000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>368000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>357000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>359000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>364000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>360000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>342000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>344000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>358000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>345000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>338000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>342000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>343000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>337000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>359000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>296000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>307000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>309000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>312000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>305000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>309000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1197000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1142000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1202000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1193000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1261000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1084000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1122000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1120000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2722000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2574000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2552000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2541000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2695000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2591000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2672000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2507000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2567000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2460000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2424000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1947000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2429000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2354000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2278000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2367000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2288000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,8 +1406,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1405,8 +1424,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1423,77 +1442,80 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>10000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>5000</v>
       </c>
       <c r="AF14" s="3">
         <v>5000</v>
       </c>
       <c r="AG14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AH14" s="3">
         <v>2000</v>
       </c>
       <c r="AI14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E15" s="3">
         <v>17000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>29000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>16000</v>
       </c>
       <c r="I15" s="3">
         <v>16000</v>
       </c>
       <c r="J15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K15" s="3">
         <v>12000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3636000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3225000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3083000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2982000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3013000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2976000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2912000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2753000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2800000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2980000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2671000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2502000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2696000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2617000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2538000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2460000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2425000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2538000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2553000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2349000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2421000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2540000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2240000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2256000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2189000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E18" s="3">
         <v>393000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>436000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>462000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>494000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>360000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>392000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>399000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>311000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>255000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>383000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>358000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>342000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>491000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>406000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>506000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>282000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>213000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-58000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>366000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>159000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>376000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>453000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-80000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>436000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>365000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>381000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>447000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>228000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>410000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>386000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>357000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,8 +1909,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1954,112 +1987,118 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E21" s="3">
         <v>410000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>454000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>478000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>523000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>376000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>408000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>411000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>324000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>267000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>396000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>371000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>356000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>504000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>420000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>520000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>297000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>228000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-42000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>382000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>175000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>393000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>472000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-60000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>454000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>386000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>401000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>469000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>251000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>432000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>407000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>377000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2067,22 +2106,22 @@
         <v>32000</v>
       </c>
       <c r="E22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="F22" s="3">
         <v>34000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>34000</v>
       </c>
       <c r="H22" s="3">
         <v>34000</v>
       </c>
       <c r="I22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="J22" s="3">
         <v>31000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>28000</v>
       </c>
       <c r="K22" s="3">
         <v>28000</v>
@@ -2103,19 +2142,19 @@
         <v>28000</v>
       </c>
       <c r="Q22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="R22" s="3">
         <v>29000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>28000</v>
       </c>
       <c r="S22" s="3">
         <v>28000</v>
       </c>
       <c r="T22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="U22" s="3">
         <v>32000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>31000</v>
       </c>
       <c r="V22" s="3">
         <v>31000</v>
@@ -2124,10 +2163,10 @@
         <v>31000</v>
       </c>
       <c r="X22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>32000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>34000</v>
       </c>
       <c r="Z22" s="3">
         <v>34000</v>
@@ -2139,239 +2178,248 @@
         <v>34000</v>
       </c>
       <c r="AC22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AD22" s="3">
         <v>35000</v>
       </c>
       <c r="AE22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>37000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>41000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>40000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>43000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>40000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E23" s="3">
         <v>361000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>402000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>427000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>460000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>326000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>361000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>371000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>283000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-51000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>227000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>355000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>330000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>314000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>462000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>378000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>478000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>250000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>182000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-89000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>335000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>127000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>342000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>419000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-114000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>402000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>330000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>346000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>410000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>187000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>370000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>343000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>317000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>78000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>85000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>89000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>93000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>68000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>78000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>74000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>44000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>60000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>64000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>58000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>94000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>66000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>91000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>37000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>31000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-28000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>62000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>20000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>64000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>77000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>66000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>60000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>55000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>104000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>43000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>98000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>83000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>76000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E26" s="3">
         <v>283000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>317000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>338000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>367000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>258000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>283000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>297000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>239000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>190000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>295000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>266000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>256000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>368000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>312000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>387000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>213000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>151000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-61000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>273000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>107000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>278000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>342000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>336000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>270000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>291000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>306000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>144000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>272000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>260000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E27" s="3">
         <v>283000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>317000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>338000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>367000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>258000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>283000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>297000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>239000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-42000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>190000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>295000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>266000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>256000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>368000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>312000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>387000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>213000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>151000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-61000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>273000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>107000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>278000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>342000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>336000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>270000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>291000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>306000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>144000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>272000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>260000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,8 +2914,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2872,11 +2932,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2884,14 +2944,17 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,8 +3193,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3202,112 +3271,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E33" s="3">
         <v>283000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>317000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>338000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>367000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>258000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>283000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>297000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>239000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-42000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>190000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>295000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>266000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>256000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>368000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>312000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>387000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>213000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>151000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-61000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>273000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>107000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>278000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>342000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>336000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>270000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>291000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>223000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>144000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>272000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>260000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E35" s="3">
         <v>283000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>317000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>338000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>367000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>258000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>283000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>297000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>239000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-42000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>190000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>295000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>266000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>256000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>368000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>312000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>387000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>213000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>151000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-61000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>273000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>107000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>278000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>342000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>336000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>270000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>291000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>223000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>144000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>272000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>260000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,139 +3784,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E41" s="3">
         <v>456000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>375000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>409000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>345000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>485000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>358000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>483000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>475000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>503000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>560000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>361000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>536000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>625000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>462000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>588000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>419000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>442000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>586000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>857000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>242000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>340000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>271000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>223000</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>310000</v>
       </c>
       <c r="AB41" s="3">
         <v>310000</v>
       </c>
       <c r="AC41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AD41" s="3">
         <v>288000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>282000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>355000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>283000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>225000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>299000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>271000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2088000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1900000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1747000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1996000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2165000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1961000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1924000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1181000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3907,112 +3996,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3671000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3494000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3816000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3432000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3442000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3211000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3521000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3126000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3158000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2986000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3210000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2892000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2945000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2799000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2954000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2652000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2607000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2527000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2755000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2502000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2481000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2504000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2690000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2476000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2365000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2400000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,35 +4210,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6502000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6258000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6105000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6021000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5856000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5888000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6005000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5899000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4219,35 +4317,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12733000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12108000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12043000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11858000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11808000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11545000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11808000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10689000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4323,254 +4424,263 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44375000</v>
+      </c>
+      <c r="E47" s="3">
         <v>45792000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>43512000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43649000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43362000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>40691000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41502000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41836000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43177000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>42137000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44280000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47106000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50328000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50236000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50265000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>48671000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>50293000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>49006000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>47757000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>44086000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>47744000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>47535000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>46747000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>45639000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>44486000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>44929000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>453000</v>
+      </c>
+      <c r="E48" s="3">
         <v>258000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>259000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>256000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>393000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>257000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>246000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>232000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>226000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>229000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>227000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>225000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>226000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>234000</v>
       </c>
       <c r="Q48" s="3">
         <v>234000</v>
       </c>
       <c r="R48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="S48" s="3">
         <v>244000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>451000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>256000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>264000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>271000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>502000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>516000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>525000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>547000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>324000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>332000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>347000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>346000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>326000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>325000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>336000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>324000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>310000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1090000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1094000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1073000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1120000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1025000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1031000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>997000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>144000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>142000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>145000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>147000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>148000</v>
       </c>
       <c r="P49" s="3">
         <v>148000</v>
@@ -4585,58 +4695,61 @@
         <v>148000</v>
       </c>
       <c r="T49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="U49" s="3">
         <v>146000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>145000</v>
       </c>
       <c r="V49" s="3">
         <v>145000</v>
       </c>
       <c r="W49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="X49" s="3">
         <v>147000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>145000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>146000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>147000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>146000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>147000</v>
       </c>
       <c r="AC49" s="3">
         <v>147000</v>
       </c>
       <c r="AD49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>149000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>147000</v>
       </c>
       <c r="AG49" s="3">
         <v>147000</v>
       </c>
       <c r="AH49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AI49" s="3">
         <v>146000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>145000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2356000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2779000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2761000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2647000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2316000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2474000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2602000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2467000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1251000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1298000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>927000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>547000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>142000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>135000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>121000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>197000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>66000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>144000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>195000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>518000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>199000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>190000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>106000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>217000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>392000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>314000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>296000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>238000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>137000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>141000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>166000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>267000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>379000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66492000</v>
+      </c>
+      <c r="E54" s="3">
         <v>67356000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>65194000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>65075000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>64711000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>61952000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>63088000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62055000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>61000000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>60215000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>62229000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63792000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66639000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66522000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>66207000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>63713000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64026000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>62775000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>62095000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58405000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>60612000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60450000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>59963000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>58477000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57152000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57259000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,35 +5360,36 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25401000</v>
+      </c>
+      <c r="E57" s="3">
         <v>24558000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23974000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23588000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23721000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22836000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22802000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22409000</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -5335,37 +5465,40 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>550000</v>
       </c>
-      <c r="G58" s="3">
-        <v>586000</v>
-      </c>
       <c r="H58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I58" s="3">
         <v>793000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>792000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>243000</v>
       </c>
       <c r="K58" s="3">
         <v>243000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
+      <c r="L58" s="3">
+        <v>243000</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -5382,8 +5515,8 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5416,13 +5549,13 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>30000</v>
       </c>
       <c r="AE58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AF58" s="3">
         <v>150000</v>
@@ -5434,144 +5567,150 @@
         <v>150000</v>
       </c>
       <c r="AI58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8746000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7659000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8209000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8146000</v>
       </c>
-      <c r="G59" s="3">
-        <v>8334000</v>
-      </c>
       <c r="H59" s="3">
+        <v>6934000</v>
+      </c>
+      <c r="I59" s="3">
         <v>7689000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7878000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7781000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19854000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16649000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17215000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17880000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19245000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18775000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18877000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18091000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18716000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17998000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17592000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16479000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17195000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17217000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16486000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15808000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14780000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14894000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34220000</v>
+      </c>
+      <c r="E60" s="3">
         <v>32217000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32183000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32284000</v>
       </c>
-      <c r="G60" s="3">
-        <v>32669000</v>
-      </c>
       <c r="H60" s="3">
+        <v>31233000</v>
+      </c>
+      <c r="I60" s="3">
         <v>31318000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31472000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30433000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5647,139 +5786,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3169000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2972000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2971000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2970000</v>
       </c>
-      <c r="G61" s="3">
-        <v>2660000</v>
-      </c>
       <c r="H61" s="3">
+        <v>2696000</v>
+      </c>
+      <c r="I61" s="3">
         <v>2480000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2384000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2539000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2780000</v>
       </c>
       <c r="M61" s="3">
         <v>2780000</v>
       </c>
       <c r="N61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="O61" s="3">
         <v>2779000</v>
       </c>
       <c r="P61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2777000</v>
       </c>
       <c r="R61" s="3">
         <v>2777000</v>
       </c>
       <c r="S61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="T61" s="3">
         <v>2776000</v>
       </c>
       <c r="U61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="V61" s="3">
         <v>2680000</v>
       </c>
       <c r="W61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="X61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>2678000</v>
       </c>
       <c r="Y61" s="3">
         <v>2678000</v>
       </c>
       <c r="Z61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>2680000</v>
       </c>
       <c r="AB61" s="3">
         <v>2680000</v>
       </c>
       <c r="AC61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AD61" s="3">
         <v>2679000</v>
       </c>
       <c r="AE61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15415000</v>
+      </c>
+      <c r="E62" s="3">
         <v>17215000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16343000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16614000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16144000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15755000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16671000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16906000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55979000</v>
+      </c>
+      <c r="E66" s="3">
         <v>56598000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55320000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55413000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54818000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53389000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54362000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53388000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52452000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52121000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52717000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52975000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53830000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53858000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53539000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51624000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51319000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>50754000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>50450000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>48043000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48397000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48327000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47876000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>47022000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>45935000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>45749000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9686000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9785000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9623000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9425000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9755000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9503000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9359000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9191000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9336000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9433000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9415000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9319000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9663000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9500000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9348000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9084000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9081000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8796000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8683000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8634000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9348000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9171000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9159000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8976000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9277000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9456000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10513000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10758000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9874000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9662000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9893000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8563000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8726000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8667000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8548000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8094000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9512000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10817000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12809000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12664000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12668000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12089000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12707000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12021000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11645000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10362000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12215000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12123000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12087000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11455000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11217000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11510000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E81" s="3">
         <v>283000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>317000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>338000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>367000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>258000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>283000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>297000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>239000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-42000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>190000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>295000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>266000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>256000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>368000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>312000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>387000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>213000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>151000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-61000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>273000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>107000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>278000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>342000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>336000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>270000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>291000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>223000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>144000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>272000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>260000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,31 +7797,32 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16000</v>
+        <v>29000</v>
       </c>
       <c r="E83" s="3">
         <v>16000</v>
       </c>
       <c r="F83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G83" s="3">
         <v>12000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>13000</v>
       </c>
       <c r="H83" s="3">
         <v>13000</v>
       </c>
       <c r="I83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J83" s="3">
         <v>12000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>13000</v>
       </c>
       <c r="K83" s="3">
         <v>13000</v>
@@ -7633,34 +7831,34 @@
         <v>13000</v>
       </c>
       <c r="M83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N83" s="3">
         <v>12000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>13000</v>
       </c>
       <c r="O83" s="3">
         <v>13000</v>
       </c>
       <c r="P83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>14000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>14000</v>
       </c>
       <c r="S83" s="3">
         <v>14000</v>
       </c>
       <c r="T83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="U83" s="3">
         <v>15000</v>
       </c>
       <c r="V83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="W83" s="3">
         <v>16000</v>
@@ -7669,43 +7867,46 @@
         <v>16000</v>
       </c>
       <c r="Y83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>17000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>18000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>21000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>20000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>22000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>23000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E89" s="3">
         <v>748000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>616000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>504000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>520000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>828000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>501000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>436000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>512000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>737000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>608000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>645000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>643000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>669000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>603000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>82000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>367000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>758000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>438000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>212000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>160000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>466000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>227000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>287000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>359000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>514000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>136000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>218000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>360000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>379000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>233000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>282000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>296000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,70 +8585,71 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-24000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-6000</v>
       </c>
       <c r="X91" s="3">
         <v>-6000</v>
@@ -8438,40 +8658,43 @@
         <v>-6000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AD91" s="3">
         <v>-38000</v>
       </c>
       <c r="AE91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-555000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-553000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>40000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-249000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-306000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-679000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-909000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>51000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-440000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-641000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-302000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-129000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-631000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-395000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-610000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>408000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-298000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-882000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-612000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1087000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-165000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-293000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>289000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-257000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>489000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>354000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,112 +9052,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>119600</v>
+      </c>
+      <c r="E96" s="3">
         <v>120100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>119900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>120300</v>
       </c>
-      <c r="G96" s="3">
-        <v>114400</v>
-      </c>
       <c r="H96" s="3">
+        <v>114000</v>
+      </c>
+      <c r="I96" s="3">
         <v>442800</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>445000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-108000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-109000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-108000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-657000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-104000</v>
       </c>
       <c r="Q96" s="3">
         <v>-104000</v>
       </c>
       <c r="R96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-100000</v>
       </c>
       <c r="T96" s="3">
         <v>-100000</v>
       </c>
       <c r="U96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-101000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-649000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-95000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-96000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-95000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AB96" s="3">
         <v>-95000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-120000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-689000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-189000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-359000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>280000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-480000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-108000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-138000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-98000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-688000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-103000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-104000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-120000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-321000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-101000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-25000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-101000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-675000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-101000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-99000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-123000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-96000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-15000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-15000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-9000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AG101" s="3">
         <v>4000</v>
       </c>
       <c r="AH101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E102" s="3">
         <v>81000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-34000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>64000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-140000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>127000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-125000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-57000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>199000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-175000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-89000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>163000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-126000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>169000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-23000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-144000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-271000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>615000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-98000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>69000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>48000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-87000</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>22000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>72000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>58000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>28000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3627000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3689000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3618000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3519000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3444000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3507000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3336000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3304000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3152000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3111000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2957000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2926000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2885000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3054000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2959000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3029000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2866000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2931000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2820000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2766000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2291000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2787000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2699000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2616000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2709000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2625000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2498000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2492000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2476000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2317000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2251000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2246000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2252000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2182000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2032000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>389000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>383000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>374000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>344000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>359000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>368000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>357000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>359000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>364000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>360000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>342000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>344000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>358000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>345000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>338000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>342000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>343000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>337000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>359000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>296000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>307000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>309000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>312000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>305000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>309000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1197000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1142000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1202000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1193000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1261000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1084000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1122000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1120000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2722000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2574000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2552000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2541000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2695000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2591000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2672000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2507000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2567000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2460000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2424000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1947000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2429000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2354000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2278000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2367000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2288000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,8 +1429,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1427,8 +1447,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1445,80 +1465,83 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>10000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>14000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>5000</v>
       </c>
       <c r="AG14" s="3">
         <v>5000</v>
       </c>
       <c r="AH14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AI14" s="3">
         <v>2000</v>
       </c>
       <c r="AJ14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AK14" s="3">
         <v>25000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E15" s="3">
         <v>16000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>16000</v>
       </c>
       <c r="J15" s="3">
         <v>16000</v>
       </c>
       <c r="K15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="L15" s="3">
         <v>12000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3246000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3636000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3225000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3083000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2982000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3013000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2976000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2912000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2753000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2800000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2980000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2671000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2502000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2696000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2617000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2538000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2460000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2425000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2538000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2553000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2349000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2421000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2540000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2240000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2256000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2189000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>381000</v>
+      </c>
+      <c r="E18" s="3">
         <v>53000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>393000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>436000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>462000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>494000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>360000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>392000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>399000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>311000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>255000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>383000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>358000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>342000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>491000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>406000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>506000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>282000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>213000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-58000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>366000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>159000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>376000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>453000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-80000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>436000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>365000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>381000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>447000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>228000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>410000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>386000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>357000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,8 +1946,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1990,115 +2024,121 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>398000</v>
+      </c>
+      <c r="E21" s="3">
         <v>69000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>410000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>454000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>478000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>523000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>376000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>408000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>411000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>324000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>267000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>396000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>371000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>356000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>504000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>420000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>520000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>297000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>228000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-42000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>382000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>175000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>393000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>472000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>454000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>386000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>401000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>469000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>251000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>432000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>407000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>377000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2109,22 +2149,22 @@
         <v>32000</v>
       </c>
       <c r="F22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="G22" s="3">
         <v>34000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>34000</v>
       </c>
       <c r="I22" s="3">
         <v>34000</v>
       </c>
       <c r="J22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K22" s="3">
         <v>31000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>28000</v>
       </c>
       <c r="L22" s="3">
         <v>28000</v>
@@ -2145,19 +2185,19 @@
         <v>28000</v>
       </c>
       <c r="R22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="S22" s="3">
         <v>29000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>28000</v>
       </c>
       <c r="T22" s="3">
         <v>28000</v>
       </c>
       <c r="U22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="V22" s="3">
         <v>32000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>31000</v>
       </c>
       <c r="W22" s="3">
         <v>31000</v>
@@ -2166,10 +2206,10 @@
         <v>31000</v>
       </c>
       <c r="Y22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>32000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>34000</v>
       </c>
       <c r="AA22" s="3">
         <v>34000</v>
@@ -2181,245 +2221,254 @@
         <v>34000</v>
       </c>
       <c r="AD22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AE22" s="3">
         <v>35000</v>
       </c>
       <c r="AF22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>37000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>41000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>40000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>40000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E23" s="3">
         <v>21000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>361000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>402000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>427000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>460000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>326000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>361000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>371000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>283000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-51000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>227000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>355000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>330000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>314000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>462000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>378000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>478000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>250000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>182000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-89000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>335000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>127000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>342000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>419000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-114000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>402000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>330000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>346000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>410000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>187000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>370000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>343000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>317000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>78000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>85000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>89000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>93000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>68000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>78000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>74000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>44000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>37000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>60000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>64000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>58000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>94000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>66000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>91000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-28000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>62000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>20000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>64000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>77000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>66000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>60000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>55000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>104000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>43000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>98000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>83000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>76000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E26" s="3">
         <v>21000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>283000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>317000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>338000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>367000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>258000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>283000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>297000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>239000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-42000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>190000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>295000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>266000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>256000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>368000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>312000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>387000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>213000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>151000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-61000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>273000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>107000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>278000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>342000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-84000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>336000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>270000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>291000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>306000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>144000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>272000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>260000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>241000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E27" s="3">
         <v>21000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>283000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>317000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>338000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>367000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>258000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>283000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>297000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>239000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-42000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>190000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>295000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>266000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>256000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>368000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>312000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>387000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>213000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>151000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-61000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>273000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>107000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>278000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>342000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>336000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>270000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>291000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>306000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>144000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>272000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>260000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>241000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2917,8 +2978,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2935,11 +2996,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2947,14 +3008,17 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,8 +3266,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3274,115 +3344,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E33" s="3">
         <v>21000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>283000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>317000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>338000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>367000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>258000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>283000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>297000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>239000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-42000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>190000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>295000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>266000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>256000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>368000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>312000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>387000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>213000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>151000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-61000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>273000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>107000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>278000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>342000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>336000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>270000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>291000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>223000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>144000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>272000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>260000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>241000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E35" s="3">
         <v>21000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>283000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>317000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>338000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>367000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>258000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>283000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>297000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>239000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-42000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>190000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>295000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>266000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>256000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>368000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>312000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>387000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>213000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>151000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-61000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>273000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>107000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>278000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>342000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>336000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>270000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>291000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>223000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>144000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>272000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>260000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>241000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,145 +3871,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E41" s="3">
         <v>472000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>456000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>375000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>409000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>345000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>485000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>358000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>483000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>475000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>503000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>560000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>361000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>536000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>625000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>462000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>588000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>419000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>442000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>586000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>857000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>242000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>340000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>271000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>223000</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>310000</v>
       </c>
       <c r="AC41" s="3">
         <v>310000</v>
       </c>
       <c r="AD41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AE41" s="3">
         <v>288000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>282000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>355000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>283000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>225000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>271000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1586000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2088000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1900000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1747000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1996000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2165000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1961000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1924000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1181000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3999,115 +4089,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3703000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3671000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3494000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3816000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3432000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3442000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3211000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3521000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3126000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3158000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2986000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3210000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2892000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2945000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2799000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2954000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2652000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2607000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2527000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2755000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2502000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2481000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2504000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2690000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2476000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2365000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2400000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,38 +4309,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6731000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6502000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6258000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6105000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6021000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5856000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5888000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6005000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5899000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4320,38 +4419,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12503000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12733000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12108000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12043000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11858000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11808000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11545000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11808000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10689000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4427,263 +4529,272 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>45334000</v>
+      </c>
+      <c r="E47" s="3">
         <v>44375000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45792000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43512000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43649000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43362000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>40691000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41502000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41836000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>43177000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>42137000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44280000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>47106000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50328000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50236000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50265000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>48671000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>50293000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>49006000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>47757000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>44086000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>47744000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>47535000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>45639000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>44486000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>44929000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E48" s="3">
         <v>453000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>258000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>259000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>256000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>393000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>257000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>246000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>232000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>226000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>229000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>227000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>225000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>226000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>234000</v>
       </c>
       <c r="R48" s="3">
         <v>234000</v>
       </c>
       <c r="S48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="T48" s="3">
         <v>244000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>451000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>256000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>264000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>271000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>502000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>516000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>525000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>547000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>324000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>332000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>347000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>346000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>326000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>325000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>336000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>324000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>310000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1145000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1181000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1090000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1094000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1073000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1120000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1025000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1031000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>997000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>144000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>142000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>145000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>147000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>148000</v>
       </c>
       <c r="Q49" s="3">
         <v>148000</v>
@@ -4698,58 +4809,61 @@
         <v>148000</v>
       </c>
       <c r="U49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="V49" s="3">
         <v>146000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>145000</v>
       </c>
       <c r="W49" s="3">
         <v>145000</v>
       </c>
       <c r="X49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>147000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>145000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>146000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>147000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>146000</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>147000</v>
       </c>
       <c r="AD49" s="3">
         <v>147000</v>
       </c>
       <c r="AE49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>149000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>147000</v>
       </c>
       <c r="AH49" s="3">
         <v>147000</v>
       </c>
       <c r="AI49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>146000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>145000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2732000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2356000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2779000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2761000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2647000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2316000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2474000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2602000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2467000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1251000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1298000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>927000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>547000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>142000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>135000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>121000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>197000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>66000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>144000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>195000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>518000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>199000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>190000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>106000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>217000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>392000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>314000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>296000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>238000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>137000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>141000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>166000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>267000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>379000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>67326000</v>
+      </c>
+      <c r="E54" s="3">
         <v>66492000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>67356000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>65194000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>65075000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>64711000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>61952000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63088000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62055000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>61000000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>60215000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>62229000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>63792000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66639000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>66522000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>66207000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>63713000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64026000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>62775000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>62095000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58405000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60612000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60450000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59963000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>58477000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57152000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57259000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,38 +5491,39 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25581000</v>
+      </c>
+      <c r="E57" s="3">
         <v>25401000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24558000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23974000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23588000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23721000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22836000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22802000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22409000</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -5468,40 +5599,43 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E58" s="3">
         <v>43000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>550000</v>
       </c>
       <c r="I58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="J58" s="3">
         <v>793000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>792000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>243000</v>
       </c>
       <c r="L58" s="3">
         <v>243000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
+      <c r="M58" s="3">
+        <v>243000</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -5518,8 +5652,8 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5552,13 +5686,13 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>30000</v>
       </c>
       <c r="AF58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AG58" s="3">
         <v>150000</v>
@@ -5570,150 +5704,156 @@
         <v>150000</v>
       </c>
       <c r="AJ58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8604000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8746000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7659000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8209000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8146000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6934000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7689000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7878000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7781000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19854000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16649000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17215000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17880000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19245000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18775000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18877000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18091000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18716000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17998000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17592000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16479000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17195000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17217000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16486000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15808000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14780000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14894000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34685000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34220000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32217000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32183000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32284000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31233000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31318000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31472000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30433000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5789,145 +5929,151 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2474000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3169000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2972000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2971000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2970000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2696000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2480000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2384000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2539000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2780000</v>
       </c>
       <c r="N61" s="3">
         <v>2780000</v>
       </c>
       <c r="O61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="P61" s="3">
         <v>2779000</v>
       </c>
       <c r="Q61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="R61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>2777000</v>
       </c>
       <c r="S61" s="3">
         <v>2777000</v>
       </c>
       <c r="T61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="U61" s="3">
         <v>2776000</v>
       </c>
       <c r="V61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="W61" s="3">
         <v>2680000</v>
       </c>
       <c r="X61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>2678000</v>
       </c>
       <c r="Z61" s="3">
         <v>2678000</v>
       </c>
       <c r="AA61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>2680000</v>
       </c>
       <c r="AC61" s="3">
         <v>2680000</v>
       </c>
       <c r="AD61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AE61" s="3">
         <v>2679000</v>
       </c>
       <c r="AF61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16500000</v>
+      </c>
+      <c r="E62" s="3">
         <v>15415000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17215000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16343000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16614000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16144000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15755000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16671000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16906000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57047000</v>
+      </c>
+      <c r="E66" s="3">
         <v>55979000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>56598000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55320000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55413000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54818000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53389000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54362000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53388000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52452000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52121000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52717000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52975000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53830000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53858000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>53539000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51624000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51319000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>50754000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50450000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48043000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48397000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48327000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>47876000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>47022000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>45935000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>45749000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9287000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9686000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9785000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9623000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9425000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9755000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9503000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9359000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9191000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9336000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9433000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9415000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9319000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9663000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9500000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9348000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9084000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9081000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8796000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8683000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8634000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9348000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9171000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9159000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8976000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9277000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9456000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10279000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10513000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10758000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9874000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9662000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9893000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8563000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8726000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8667000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8548000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8094000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9512000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10817000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12809000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12664000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12668000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12089000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12707000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12021000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11645000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10362000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12215000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12123000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12087000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11455000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11217000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11510000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E81" s="3">
         <v>21000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>283000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>317000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>338000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>367000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>258000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>283000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>297000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>239000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-42000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>190000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>295000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>266000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>256000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>368000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>312000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>387000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>213000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>151000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-61000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>273000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>107000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>278000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>342000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>336000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>270000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>291000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>223000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>144000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>272000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>260000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>241000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,34 +7996,35 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E83" s="3">
         <v>29000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>16000</v>
       </c>
       <c r="F83" s="3">
         <v>16000</v>
       </c>
       <c r="G83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H83" s="3">
         <v>12000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>13000</v>
       </c>
       <c r="I83" s="3">
         <v>13000</v>
       </c>
       <c r="J83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K83" s="3">
         <v>12000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>13000</v>
       </c>
       <c r="L83" s="3">
         <v>13000</v>
@@ -7834,34 +8033,34 @@
         <v>13000</v>
       </c>
       <c r="N83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O83" s="3">
         <v>12000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>13000</v>
       </c>
       <c r="P83" s="3">
         <v>13000</v>
       </c>
       <c r="Q83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="R83" s="3">
         <v>14000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>14000</v>
       </c>
       <c r="T83" s="3">
         <v>14000</v>
       </c>
       <c r="U83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="V83" s="3">
         <v>15000</v>
       </c>
       <c r="W83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="X83" s="3">
         <v>16000</v>
@@ -7870,43 +8069,46 @@
         <v>16000</v>
       </c>
       <c r="Z83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>17000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>18000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>21000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>23000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>22000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>20000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>638000</v>
+      </c>
+      <c r="E89" s="3">
         <v>703000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>748000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>616000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>504000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>520000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>828000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>501000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>436000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>512000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>737000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>608000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>645000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>643000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>669000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>603000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>82000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>367000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>758000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>438000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>212000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>160000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>466000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>227000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>287000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>359000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>514000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>136000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>218000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>360000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>379000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>233000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>282000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>296000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,73 +8806,74 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-6000</v>
       </c>
       <c r="Y91" s="3">
         <v>-6000</v>
@@ -8661,40 +8882,43 @@
         <v>-6000</v>
       </c>
       <c r="AA91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AE91" s="3">
         <v>-38000</v>
       </c>
       <c r="AF91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-555000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-553000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>40000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-249000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-306000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-679000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-909000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>51000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-440000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-641000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-302000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-129000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-631000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-395000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-610000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>408000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-298000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-882000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-612000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1087000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-165000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-293000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>289000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-257000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>489000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>354000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9286,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E96" s="3">
         <v>119600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>120100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>119900</v>
       </c>
-      <c r="G96" s="3">
-        <v>120300</v>
-      </c>
       <c r="H96" s="3">
+        <v>667000</v>
+      </c>
+      <c r="I96" s="3">
         <v>114000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>442800</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>445000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-108000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-109000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-108000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-657000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-104000</v>
       </c>
       <c r="R96" s="3">
         <v>-104000</v>
       </c>
       <c r="S96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-100000</v>
       </c>
       <c r="U96" s="3">
         <v>-100000</v>
       </c>
       <c r="V96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-101000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-649000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-95000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-96000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-95000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AC96" s="3">
         <v>-95000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-722000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-119000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-120000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-689000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-189000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-359000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>280000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-480000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-108000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-138000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-98000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-688000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-103000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-104000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-120000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-321000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-101000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-25000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-101000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-675000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-101000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-99000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-123000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-96000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-134000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-15000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-15000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>9000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AH101" s="3">
         <v>4000</v>
       </c>
       <c r="AI101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>16000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>81000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-34000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>64000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-140000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>127000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-125000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-57000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>199000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-175000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-89000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>163000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-126000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>169000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-23000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-144000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-271000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>615000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-98000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>69000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>48000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-87000</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>22000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>72000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>58000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3717000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3627000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3689000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3618000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3519000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3444000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3507000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3336000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3304000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3152000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3111000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2957000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2926000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2885000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3054000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2959000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3029000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2866000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2931000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2820000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2766000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2291000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2787000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2699000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2616000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2709000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2625000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2554000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2498000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2492000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2476000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2317000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2251000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2246000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2252000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2182000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2032000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>389000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>383000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>374000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>344000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>359000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>368000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>357000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>359000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>364000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>360000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>342000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>344000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>358000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>345000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>338000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>342000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>343000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>337000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>359000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>296000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>307000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>309000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>312000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>305000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>309000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1163000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1129000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1197000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1142000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1202000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1193000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1261000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1084000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1122000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1120000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2722000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2574000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2552000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2541000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2695000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2591000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2672000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2507000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2567000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2460000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2424000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1947000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2429000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2354000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2278000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2367000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2288000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1450,8 +1470,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1468,83 +1488,86 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>10000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>5000</v>
       </c>
       <c r="AH14" s="3">
         <v>5000</v>
       </c>
       <c r="AI14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AJ14" s="3">
         <v>2000</v>
       </c>
       <c r="AK14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AL14" s="3">
         <v>25000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E15" s="3">
         <v>17000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>17000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>16000</v>
       </c>
       <c r="K15" s="3">
         <v>16000</v>
       </c>
       <c r="L15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="M15" s="3">
         <v>12000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3306000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3246000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3636000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3225000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3083000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2982000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3013000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2976000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2912000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2753000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2800000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2980000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2671000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2502000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2696000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2617000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2538000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2460000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2425000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2538000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2553000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2349000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2421000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2540000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2240000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2256000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2189000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E18" s="3">
         <v>381000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>53000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>393000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>436000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>462000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>494000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>360000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>392000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>399000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>311000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>255000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>383000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>358000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>342000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>491000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>406000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>506000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>282000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>213000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>366000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>159000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>376000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>453000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-80000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>436000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>365000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>381000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>447000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>228000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>410000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>386000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>357000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,8 +1983,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -2027,123 +2061,129 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E21" s="3">
         <v>398000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>69000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>410000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>454000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>478000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>523000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>376000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>408000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>411000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>324000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>267000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>396000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>371000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>356000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>504000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>420000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>520000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>297000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>228000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>382000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>175000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>393000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>472000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>454000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>386000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>401000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>469000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>251000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>432000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>407000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>377000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="E22" s="3">
         <v>32000</v>
@@ -2152,22 +2192,22 @@
         <v>32000</v>
       </c>
       <c r="G22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="H22" s="3">
         <v>34000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>34000</v>
       </c>
       <c r="J22" s="3">
         <v>34000</v>
       </c>
       <c r="K22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="L22" s="3">
         <v>31000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>28000</v>
       </c>
       <c r="M22" s="3">
         <v>28000</v>
@@ -2188,19 +2228,19 @@
         <v>28000</v>
       </c>
       <c r="S22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="T22" s="3">
         <v>29000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>28000</v>
       </c>
       <c r="U22" s="3">
         <v>28000</v>
       </c>
       <c r="V22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="W22" s="3">
         <v>32000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>31000</v>
       </c>
       <c r="X22" s="3">
         <v>31000</v>
@@ -2209,10 +2249,10 @@
         <v>31000</v>
       </c>
       <c r="Z22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>32000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>34000</v>
       </c>
       <c r="AB22" s="3">
         <v>34000</v>
@@ -2224,251 +2264,260 @@
         <v>34000</v>
       </c>
       <c r="AE22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AF22" s="3">
         <v>35000</v>
       </c>
       <c r="AG22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>37000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>41000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>40000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>43000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>40000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>380000</v>
+      </c>
+      <c r="E23" s="3">
         <v>349000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>361000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>402000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>427000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>460000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>326000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>361000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>371000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>283000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-51000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>227000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>355000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>330000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>314000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>462000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>378000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>478000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>250000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>182000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-89000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>335000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>127000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>342000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>419000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-114000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>402000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>330000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>346000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>410000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>187000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>370000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>343000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>317000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E24" s="3">
         <v>75000</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>78000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>85000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>89000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>93000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>68000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>78000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>74000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>44000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>37000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>60000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>64000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>58000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>94000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>66000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>91000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>37000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>62000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>20000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>64000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>77000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>66000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>60000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>55000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>104000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>43000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>98000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>83000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>76000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E26" s="3">
         <v>274000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>283000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>317000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>338000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>367000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>258000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>283000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>297000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>239000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-42000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>190000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>295000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>266000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>256000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>368000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>312000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>387000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>213000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>151000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>273000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>107000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>278000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>342000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>336000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>270000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>291000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>306000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>144000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>260000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>241000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E27" s="3">
         <v>274000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>283000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>317000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>338000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>367000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>258000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>283000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>297000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>239000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-42000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>190000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>295000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>266000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>256000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>368000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>312000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>387000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>213000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>151000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>273000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>107000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>278000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>342000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>336000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>270000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>291000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>306000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>144000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>260000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>241000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2981,8 +3042,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2999,11 +3060,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3011,14 +3072,17 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,8 +3339,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3347,118 +3417,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E33" s="3">
         <v>274000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>283000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>317000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>338000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>367000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>258000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>283000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>297000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>239000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-42000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>190000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>295000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>266000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>256000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>368000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>312000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>387000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>213000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>151000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>273000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>107000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>278000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>342000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>336000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>270000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>291000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>223000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>144000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>260000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>241000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E35" s="3">
         <v>274000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>283000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>317000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>338000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>367000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>258000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>283000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>297000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>239000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-42000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>190000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>295000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>266000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>256000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>368000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>312000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>387000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>213000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>151000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>273000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>107000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>278000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>342000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>336000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>270000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>291000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>223000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>144000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>260000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>241000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,151 +3958,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E41" s="3">
         <v>483000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>472000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>456000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>375000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>409000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>345000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>485000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>358000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>483000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>475000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>503000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>560000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>361000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>536000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>625000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>462000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>588000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>419000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>442000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>586000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>857000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>242000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>340000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>271000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>223000</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>310000</v>
       </c>
       <c r="AD41" s="3">
         <v>310000</v>
       </c>
       <c r="AE41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AF41" s="3">
         <v>288000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>282000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>355000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>283000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>225000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>299000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>271000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1586000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2088000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1900000</v>
       </c>
-      <c r="G42" s="3">
-        <v>1747000</v>
-      </c>
       <c r="H42" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="I42" s="3">
         <v>1996000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2165000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1961000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1924000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1181000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4092,118 +4182,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4062000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3703000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3671000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3494000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3816000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3432000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3442000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3211000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3521000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3126000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3158000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2986000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3210000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2892000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2945000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2799000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2954000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2652000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2607000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2527000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2755000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2502000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2481000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2504000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2690000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2476000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2365000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2400000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,41 +4408,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6878000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6731000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6502000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6258000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6105000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6021000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5856000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5888000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6005000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5899000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4422,41 +4521,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13056000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12503000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12733000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12108000</v>
       </c>
-      <c r="G46" s="3">
-        <v>12043000</v>
-      </c>
       <c r="H46" s="3">
+        <v>12047000</v>
+      </c>
+      <c r="I46" s="3">
         <v>11858000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11808000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11545000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11808000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10689000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,272 +4634,281 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46265000</v>
+      </c>
+      <c r="E47" s="3">
         <v>45334000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>44375000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45792000</v>
       </c>
-      <c r="G47" s="3">
-        <v>43512000</v>
-      </c>
       <c r="H47" s="3">
+        <v>43508000</v>
+      </c>
+      <c r="I47" s="3">
         <v>43649000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43362000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40691000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41502000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>41836000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>43177000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>42137000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44280000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>47106000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50328000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50236000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>50265000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>48671000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>50293000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>49006000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>47757000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>44086000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>47744000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>47535000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>45639000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>44486000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>44929000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>297000</v>
+      </c>
+      <c r="E48" s="3">
         <v>291000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>453000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>258000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>259000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>256000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>393000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>257000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>246000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>232000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>226000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>229000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>227000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>225000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>226000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>234000</v>
       </c>
       <c r="S48" s="3">
         <v>234000</v>
       </c>
       <c r="T48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="U48" s="3">
         <v>244000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>451000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>256000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>264000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>271000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>502000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>516000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>525000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>547000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>324000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>332000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>347000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>346000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>326000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>325000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>336000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>324000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>310000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1169000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1145000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1181000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1090000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1094000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1073000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1120000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1025000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1031000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>997000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>144000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>142000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>145000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>147000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>148000</v>
       </c>
       <c r="R49" s="3">
         <v>148000</v>
@@ -4812,58 +4923,61 @@
         <v>148000</v>
       </c>
       <c r="V49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="W49" s="3">
         <v>146000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>145000</v>
       </c>
       <c r="X49" s="3">
         <v>145000</v>
       </c>
       <c r="Y49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>147000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>145000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>146000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>147000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>146000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>147000</v>
       </c>
       <c r="AE49" s="3">
         <v>147000</v>
       </c>
       <c r="AF49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>149000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>147000</v>
       </c>
       <c r="AI49" s="3">
         <v>147000</v>
       </c>
       <c r="AJ49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AK49" s="3">
         <v>146000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>145000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2909000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2732000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2356000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2779000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2761000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2647000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2316000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2474000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2602000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2467000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1251000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1298000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>927000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>547000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>142000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>135000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>121000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>197000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>66000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>144000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>195000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>518000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>199000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>190000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>106000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>217000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>392000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>314000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>296000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>238000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>137000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>141000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>267000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>379000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68936000</v>
+      </c>
+      <c r="E54" s="3">
         <v>67326000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>66492000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>67356000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>65194000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>65075000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64711000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>61952000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>63088000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62055000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>61000000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>60215000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>62229000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>63792000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>66639000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>66522000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66207000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>63713000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64026000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>62775000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>62095000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58405000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60612000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>60450000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59963000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>58477000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57152000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57259000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,41 +5622,42 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26203000</v>
+      </c>
+      <c r="E57" s="3">
         <v>25581000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25401000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24558000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23974000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23588000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23721000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22836000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22802000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22409000</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -5602,8 +5733,11 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5611,34 +5745,34 @@
         <v>500000</v>
       </c>
       <c r="E58" s="3">
+        <v>500000</v>
+      </c>
+      <c r="F58" s="3">
         <v>43000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>550000</v>
       </c>
       <c r="J58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="K58" s="3">
         <v>793000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>792000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>243000</v>
       </c>
       <c r="M58" s="3">
         <v>243000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
+      <c r="N58" s="3">
+        <v>243000</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -5655,8 +5789,8 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5689,13 +5823,13 @@
         <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>30000</v>
       </c>
       <c r="AG58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AH58" s="3">
         <v>150000</v>
@@ -5707,156 +5841,162 @@
         <v>150000</v>
       </c>
       <c r="AK58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8690000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8604000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8746000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7659000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8209000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8146000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6934000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7689000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7878000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7781000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19854000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16649000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17215000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17880000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19245000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18775000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18877000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18091000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18716000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17998000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17592000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16479000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17195000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17217000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16486000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15808000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14780000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14894000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35393000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34685000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34220000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32217000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32183000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32284000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31233000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31318000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31472000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30433000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5932,151 +6072,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2475000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2474000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3169000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2972000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2971000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2970000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2696000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2480000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2384000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2539000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2780000</v>
       </c>
       <c r="O61" s="3">
         <v>2780000</v>
       </c>
       <c r="P61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="Q61" s="3">
         <v>2779000</v>
       </c>
       <c r="R61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="S61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>2777000</v>
       </c>
       <c r="T61" s="3">
         <v>2777000</v>
       </c>
       <c r="U61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="V61" s="3">
         <v>2776000</v>
       </c>
       <c r="W61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="X61" s="3">
         <v>2680000</v>
       </c>
       <c r="Y61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>2678000</v>
       </c>
       <c r="AA61" s="3">
         <v>2678000</v>
       </c>
       <c r="AB61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>2680000</v>
       </c>
       <c r="AD61" s="3">
         <v>2680000</v>
       </c>
       <c r="AE61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AF61" s="3">
         <v>2679000</v>
       </c>
       <c r="AG61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16786000</v>
+      </c>
+      <c r="E62" s="3">
         <v>16500000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15415000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17215000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16343000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16614000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16144000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15755000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16671000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16906000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58275000</v>
+      </c>
+      <c r="E66" s="3">
         <v>57047000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55979000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>56598000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55320000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>55413000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54818000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53389000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54362000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53388000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52452000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52121000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52717000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52975000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53830000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>53858000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>53539000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51624000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51319000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50754000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>50450000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48043000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48397000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>48327000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>47876000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>47022000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>45935000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>45749000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9460000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9287000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9686000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9785000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9623000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9425000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9755000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9503000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9359000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9191000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9336000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9433000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9415000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9319000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9663000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9500000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9348000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9084000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9081000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8796000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8683000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8634000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9348000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9171000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9159000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8976000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9277000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9456000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10661000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10279000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10513000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10758000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9874000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9662000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9893000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8563000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8726000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8667000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8548000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8094000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9512000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10817000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12809000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12664000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12668000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12089000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12707000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12021000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11645000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10362000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12215000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12123000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12087000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11455000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11217000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11510000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E81" s="3">
         <v>274000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>283000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>317000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>338000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>367000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>258000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>283000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>297000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>239000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-42000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>190000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>295000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>266000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>256000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>368000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>312000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>387000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>213000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>151000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>273000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>107000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>278000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>342000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>336000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>270000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>291000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>223000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>144000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>260000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>241000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,37 +8195,38 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E83" s="3">
         <v>16000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>29000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>16000</v>
       </c>
       <c r="G83" s="3">
         <v>16000</v>
       </c>
       <c r="H83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I83" s="3">
         <v>12000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>13000</v>
       </c>
       <c r="J83" s="3">
         <v>13000</v>
       </c>
       <c r="K83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L83" s="3">
         <v>12000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>13000</v>
       </c>
       <c r="M83" s="3">
         <v>13000</v>
@@ -8036,34 +8235,34 @@
         <v>13000</v>
       </c>
       <c r="O83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="P83" s="3">
         <v>12000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>13000</v>
       </c>
       <c r="Q83" s="3">
         <v>13000</v>
       </c>
       <c r="R83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="S83" s="3">
         <v>14000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>14000</v>
       </c>
       <c r="U83" s="3">
         <v>14000</v>
       </c>
       <c r="V83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="W83" s="3">
         <v>15000</v>
       </c>
       <c r="X83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="Y83" s="3">
         <v>16000</v>
@@ -8072,43 +8271,46 @@
         <v>16000</v>
       </c>
       <c r="AA83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>17000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>18000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>23000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>21000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>20000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E89" s="3">
         <v>638000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>703000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>748000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>616000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>504000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>520000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>828000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>501000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>436000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>512000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>737000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>608000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>645000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>643000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>669000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>603000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>82000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>367000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>758000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>438000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>212000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>160000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>466000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>227000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>287000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>359000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>514000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>136000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>218000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>360000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>379000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>233000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>282000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>296000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,76 +9027,77 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-6000</v>
       </c>
       <c r="Z91" s="3">
         <v>-6000</v>
@@ -8885,40 +9106,43 @@
         <v>-6000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AF91" s="3">
         <v>-38000</v>
       </c>
       <c r="AG91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-559000</v>
+      </c>
+      <c r="E94" s="3">
         <v>88000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-555000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-553000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>40000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-249000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-306000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-679000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-909000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>51000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-440000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-641000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-302000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-631000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-395000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-610000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>408000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-298000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-882000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-612000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1087000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-165000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>289000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-257000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>489000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>354000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9520,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>125600</v>
+      </c>
+      <c r="E96" s="3">
         <v>125900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>119600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>120100</v>
       </c>
-      <c r="G96" s="3">
-        <v>119900</v>
-      </c>
       <c r="H96" s="3">
+        <v>119000</v>
+      </c>
+      <c r="I96" s="3">
         <v>667000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>114000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>442800</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>445000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-108000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-109000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-108000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-657000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-104000</v>
       </c>
       <c r="S96" s="3">
         <v>-104000</v>
       </c>
       <c r="T96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-100000</v>
       </c>
       <c r="V96" s="3">
         <v>-100000</v>
       </c>
       <c r="W96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-101000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-649000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-95000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-96000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-95000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AD96" s="3">
         <v>-95000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-125000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-722000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-119000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-120000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-689000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-189000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-359000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>280000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-480000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-108000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-138000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-98000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-688000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-103000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-104000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-120000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-321000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-101000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-101000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-675000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-101000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-123000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-96000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-134000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>4000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-15000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-15000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>9000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AI101" s="3">
         <v>4000</v>
       </c>
       <c r="AJ101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AK101" s="3">
         <v>1000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>81000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-34000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>64000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-140000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>127000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-125000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-57000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>199000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-175000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-89000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>163000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-126000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>169000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-144000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-271000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>615000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-98000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>69000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>48000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-87000</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>22000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>72000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>58000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>28000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3828000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3817000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3717000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3627000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3689000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3618000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3519000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3444000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3507000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3336000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3304000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3152000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3111000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2957000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2926000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2885000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3054000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2959000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3029000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2866000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2931000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2820000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2766000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2291000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2787000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2699000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2616000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2709000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2625000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2625000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2515000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2554000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2498000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2492000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2476000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2317000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2251000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2246000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2252000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2182000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2032000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>389000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>383000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>374000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>344000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>359000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>368000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>357000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>359000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>364000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>360000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>342000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>344000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>358000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>345000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>338000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>342000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>343000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>337000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>359000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>296000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>307000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>309000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>312000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>305000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>309000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1203000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1302000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1163000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1129000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1197000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1142000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1202000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1193000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1261000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1084000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1122000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1120000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2722000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2574000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2552000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2541000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2695000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2591000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2672000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2507000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2567000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2460000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2424000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1947000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2429000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2354000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2278000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2367000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2288000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,8 +1497,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1496,8 +1515,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1514,89 +1533,92 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>10000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>14000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>12000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>5000</v>
       </c>
       <c r="AJ14" s="3">
         <v>5000</v>
       </c>
       <c r="AK14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AL14" s="3">
         <v>2000</v>
       </c>
       <c r="AM14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AN14" s="3">
         <v>25000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="E15" s="3">
         <v>18000</v>
       </c>
       <c r="F15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="G15" s="3">
         <v>17000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>29000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>16000</v>
       </c>
       <c r="M15" s="3">
         <v>16000</v>
       </c>
       <c r="N15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="O15" s="3">
         <v>12000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3414000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3268000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3306000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3246000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3636000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3225000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3083000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2982000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3013000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2976000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2912000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2753000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2800000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2980000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2671000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2502000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2696000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2617000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2538000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2460000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2425000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2538000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2553000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2349000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2421000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2540000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2240000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2256000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2189000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E18" s="3">
         <v>549000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>411000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>381000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>53000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>393000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>436000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>462000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>494000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>360000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>392000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>399000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>311000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>255000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>383000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>358000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>342000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>491000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>406000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>506000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>282000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>213000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>366000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>159000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>376000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>453000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-80000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>436000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>365000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>381000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>447000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>228000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>410000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>386000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>357000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,8 +2056,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -2101,124 +2134,130 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>431000</v>
+      </c>
+      <c r="E21" s="3">
         <v>567000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>429000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>398000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>69000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>410000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>454000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>478000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>523000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>376000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>408000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>411000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>324000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>267000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>396000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>371000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>356000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>504000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>420000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>520000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>297000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>228000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>382000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>175000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>393000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>472000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-60000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>454000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>386000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>401000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>469000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>251000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>432000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>407000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>377000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2226,10 +2265,10 @@
         <v>36000</v>
       </c>
       <c r="E22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F22" s="3">
         <v>31000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>32000</v>
       </c>
       <c r="G22" s="3">
         <v>32000</v>
@@ -2238,22 +2277,22 @@
         <v>32000</v>
       </c>
       <c r="I22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="J22" s="3">
         <v>34000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>34000</v>
       </c>
       <c r="L22" s="3">
         <v>34000</v>
       </c>
       <c r="M22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="N22" s="3">
         <v>31000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>28000</v>
       </c>
       <c r="O22" s="3">
         <v>28000</v>
@@ -2274,19 +2313,19 @@
         <v>28000</v>
       </c>
       <c r="U22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="V22" s="3">
         <v>29000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>28000</v>
       </c>
       <c r="W22" s="3">
         <v>28000</v>
       </c>
       <c r="X22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>32000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>31000</v>
       </c>
       <c r="Z22" s="3">
         <v>31000</v>
@@ -2295,10 +2334,10 @@
         <v>31000</v>
       </c>
       <c r="AB22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>32000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>34000</v>
       </c>
       <c r="AD22" s="3">
         <v>34000</v>
@@ -2310,263 +2349,272 @@
         <v>34000</v>
       </c>
       <c r="AG22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AH22" s="3">
         <v>35000</v>
       </c>
       <c r="AI22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>37000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>41000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>40000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>43000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>40000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E23" s="3">
         <v>513000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>380000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>349000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>361000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>402000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>427000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>460000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>326000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>361000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>371000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>283000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>227000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>355000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>330000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>314000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>462000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>378000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>478000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>250000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>182000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-89000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>335000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>127000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>342000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>419000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-114000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>402000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>330000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>346000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>410000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>187000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>370000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>343000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>317000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E24" s="3">
         <v>110000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>81000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>75000</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>78000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>85000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>89000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>93000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>68000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>78000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>74000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>44000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>60000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>64000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>58000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>94000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>66000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>91000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>37000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>62000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>20000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>64000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>77000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>66000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>60000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>55000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>43000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>98000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>83000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>76000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E26" s="3">
         <v>403000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>299000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>274000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>283000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>317000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>338000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>367000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>258000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>283000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>297000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>239000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>190000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>295000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>266000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>256000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>368000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>312000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>387000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>213000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>151000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>273000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>107000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>278000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>342000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>336000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>270000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>291000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>306000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>144000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>272000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>260000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>241000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E27" s="3">
         <v>403000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>299000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>274000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>283000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>317000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>338000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>367000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>258000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>283000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>297000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>239000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>190000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>295000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>266000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>256000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>368000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>312000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>387000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>213000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>151000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>273000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>107000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>278000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>342000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>336000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>270000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>291000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>306000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>144000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>272000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>260000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>241000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3109,8 +3169,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3127,11 +3187,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3139,14 +3199,17 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,8 +3484,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3493,124 +3562,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E33" s="3">
         <v>403000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>299000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>274000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>283000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>317000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>338000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>367000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>258000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>283000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>297000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>239000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>190000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>295000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>266000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>256000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>368000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>312000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>387000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>213000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>151000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>273000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>107000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>278000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>342000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>336000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>270000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>291000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>223000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>144000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>272000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>260000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>241000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E35" s="3">
         <v>403000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>299000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>274000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>283000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>317000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>338000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>367000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>258000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>283000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>297000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>239000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>190000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>295000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>266000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>256000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>368000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>312000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>387000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>213000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>151000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>273000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>107000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>278000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>342000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>336000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>270000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>291000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>223000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>144000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>272000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>260000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>241000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,163 +4131,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E41" s="3">
         <v>483000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>373000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>483000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>472000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>456000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>375000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>409000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>345000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>485000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>358000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>483000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>475000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>503000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>560000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>361000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>536000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>625000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>462000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>588000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>419000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>442000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>586000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>857000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>242000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>340000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>271000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>223000</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>310000</v>
       </c>
       <c r="AF41" s="3">
         <v>310000</v>
       </c>
       <c r="AG41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AH41" s="3">
         <v>288000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>282000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>355000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>283000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>225000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>299000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>271000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2320000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2258000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1743000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1586000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2088000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1900000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1751000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1996000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2165000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1961000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1924000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1181000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4278,124 +4367,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3739000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3666000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4062000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3703000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3671000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3494000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3816000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3432000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3442000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3211000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3521000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3126000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3158000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2986000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3210000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2892000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2945000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2799000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2954000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2652000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2607000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2527000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2755000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2502000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2481000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2504000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2690000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2476000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2365000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2400000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,47 +4605,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6861000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6925000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6878000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6731000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6502000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6258000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6105000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6021000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5856000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5888000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6005000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5899000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4626,47 +4724,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13345000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13332000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13056000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12503000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12733000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12108000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12047000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11858000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11808000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11545000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11808000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10689000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4742,290 +4843,299 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47048000</v>
+      </c>
+      <c r="E47" s="3">
         <v>47223000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46265000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45334000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44375000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45792000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43508000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43649000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43362000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>40691000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>41502000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41836000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>43177000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>42137000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44280000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>47106000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>50328000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>50236000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>50265000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>48671000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>50293000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>49006000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>47757000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>44086000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>47744000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>47535000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>45639000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>44486000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>44929000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>430000</v>
+      </c>
+      <c r="E48" s="3">
         <v>283000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>297000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>291000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>453000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>258000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>259000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>256000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>393000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>257000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>246000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>232000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>226000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>229000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>227000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>225000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>226000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>234000</v>
       </c>
       <c r="U48" s="3">
         <v>234000</v>
       </c>
       <c r="V48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="W48" s="3">
         <v>244000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>451000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>256000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>264000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>271000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>502000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>516000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>525000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>547000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>324000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>332000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>347000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>346000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>326000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>325000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>336000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>324000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>310000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1134000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1133000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1169000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1145000</v>
       </c>
-      <c r="G49" s="3">
-        <v>1181000</v>
-      </c>
       <c r="H49" s="3">
+        <v>1104000</v>
+      </c>
+      <c r="I49" s="3">
         <v>1090000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1094000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1073000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1120000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1025000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1031000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>997000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>144000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>142000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>145000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>147000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>148000</v>
       </c>
       <c r="T49" s="3">
         <v>148000</v>
@@ -5040,58 +5150,61 @@
         <v>148000</v>
       </c>
       <c r="X49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>146000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>145000</v>
       </c>
       <c r="Z49" s="3">
         <v>145000</v>
       </c>
       <c r="AA49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>147000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>145000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>146000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>147000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>146000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>147000</v>
       </c>
       <c r="AG49" s="3">
         <v>147000</v>
       </c>
       <c r="AH49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AI49" s="3">
         <v>149000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>147000</v>
       </c>
       <c r="AK49" s="3">
         <v>147000</v>
       </c>
       <c r="AL49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AM49" s="3">
         <v>146000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>145000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2612000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2805000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2909000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2732000</v>
       </c>
-      <c r="G52" s="3">
-        <v>2356000</v>
-      </c>
       <c r="H52" s="3">
+        <v>2433000</v>
+      </c>
+      <c r="I52" s="3">
         <v>2779000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2761000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2647000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2316000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2474000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2602000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2467000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1251000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>927000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>547000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>142000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>135000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>121000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>197000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>66000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>144000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>195000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>518000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>199000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>190000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>106000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>217000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>392000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>314000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>296000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>238000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>137000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>141000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>166000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>267000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>379000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>69443000</v>
+      </c>
+      <c r="E54" s="3">
         <v>69756000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68936000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>67326000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>66492000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>67356000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>65194000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>65075000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64711000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>61952000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>63088000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>62055000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>61000000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>60215000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62229000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>63792000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66639000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>66522000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66207000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>63713000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64026000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>62775000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62095000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>58405000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>60612000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60450000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>59963000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>58477000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57152000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>57259000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,47 +5883,48 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27069000</v>
+      </c>
+      <c r="E57" s="3">
         <v>26911000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26203000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25581000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>25401000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24558000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23974000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23588000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23721000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22836000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22802000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22409000</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -5870,13 +6000,16 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500000</v>
+        <v>34000</v>
       </c>
       <c r="E58" s="3">
         <v>500000</v>
@@ -5885,7 +6018,7 @@
         <v>500000</v>
       </c>
       <c r="G58" s="3">
-        <v>43000</v>
+        <v>500000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -5894,25 +6027,25 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>550000</v>
       </c>
       <c r="L58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="M58" s="3">
         <v>793000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>792000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>243000</v>
       </c>
       <c r="O58" s="3">
         <v>243000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
+      <c r="P58" s="3">
+        <v>243000</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
@@ -5929,8 +6062,8 @@
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5963,13 +6096,13 @@
         <v>0</v>
       </c>
       <c r="AG58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AH58" s="3">
         <v>30000</v>
       </c>
       <c r="AI58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AJ58" s="3">
         <v>150000</v>
@@ -5981,168 +6114,174 @@
         <v>150000</v>
       </c>
       <c r="AM58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9035000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7978000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8690000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8604000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8746000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7659000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8209000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8146000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6934000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7689000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7878000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7781000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19854000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16649000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17215000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17880000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19245000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18775000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18877000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18091000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18716000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17998000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17592000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16479000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17195000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17217000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>16486000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15808000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14780000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14894000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36171000</v>
+      </c>
+      <c r="E60" s="3">
         <v>35389000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35393000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34685000</v>
       </c>
-      <c r="G60" s="3">
-        <v>34220000</v>
-      </c>
       <c r="H60" s="3">
+        <v>34177000</v>
+      </c>
+      <c r="I60" s="3">
         <v>32217000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32183000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32284000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31233000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31318000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31472000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30433000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6218,163 +6357,169 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3155000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2970000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2475000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2474000</v>
       </c>
-      <c r="G61" s="3">
-        <v>3169000</v>
-      </c>
       <c r="H61" s="3">
+        <v>3212000</v>
+      </c>
+      <c r="I61" s="3">
         <v>2972000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2971000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2970000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2696000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2480000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2384000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2539000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2780000</v>
       </c>
       <c r="Q61" s="3">
         <v>2780000</v>
       </c>
       <c r="R61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="S61" s="3">
         <v>2779000</v>
       </c>
       <c r="T61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="U61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>2777000</v>
       </c>
       <c r="V61" s="3">
         <v>2777000</v>
       </c>
       <c r="W61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="X61" s="3">
         <v>2776000</v>
       </c>
       <c r="Y61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="Z61" s="3">
         <v>2680000</v>
       </c>
       <c r="AA61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>2678000</v>
       </c>
       <c r="AC61" s="3">
         <v>2678000</v>
       </c>
       <c r="AD61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>2680000</v>
       </c>
       <c r="AF61" s="3">
         <v>2680000</v>
       </c>
       <c r="AG61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AH61" s="3">
         <v>2679000</v>
       </c>
       <c r="AI61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15718000</v>
+      </c>
+      <c r="E62" s="3">
         <v>16181000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16786000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16500000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15415000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17215000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16343000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16614000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16144000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15755000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16671000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16906000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6595,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57822000</v>
+      </c>
+      <c r="E66" s="3">
         <v>58434000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>58275000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57047000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55979000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>56598000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55320000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55413000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54818000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53389000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54362000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53388000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52452000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52121000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>52717000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52975000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>53830000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>53858000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>53539000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51624000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51319000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>50754000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>50450000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>48043000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>48397000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>48327000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>47876000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>47022000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>45935000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>45749000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9915000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9739000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9460000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9287000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9686000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9785000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9623000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9425000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9755000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9503000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9359000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9191000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9336000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9433000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9415000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9319000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9663000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9500000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9348000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9084000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9081000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8796000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8683000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8634000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9348000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9171000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9159000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8976000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9277000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9456000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11621000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11322000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10661000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10279000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10513000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10758000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9874000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9662000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9893000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8563000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8726000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8667000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8548000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8094000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9512000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10817000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12809000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12664000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12668000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12089000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12707000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12021000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11645000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10362000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12215000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12123000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12087000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11455000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11217000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11510000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E81" s="3">
         <v>403000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>299000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>274000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>283000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>317000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>338000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>367000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>258000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>283000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>297000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>239000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>190000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>295000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>266000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>256000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>368000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>312000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>387000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>213000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>151000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>273000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>107000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>278000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>342000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>336000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>270000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>291000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>223000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>144000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>272000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>260000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>241000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,43 +8592,44 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E83" s="3">
         <v>17000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>16000</v>
       </c>
       <c r="I83" s="3">
         <v>16000</v>
       </c>
       <c r="J83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K83" s="3">
         <v>12000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>13000</v>
       </c>
       <c r="L83" s="3">
         <v>13000</v>
       </c>
       <c r="M83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N83" s="3">
         <v>12000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>13000</v>
       </c>
       <c r="O83" s="3">
         <v>13000</v>
@@ -8440,34 +8638,34 @@
         <v>13000</v>
       </c>
       <c r="Q83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="R83" s="3">
         <v>12000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>13000</v>
       </c>
       <c r="S83" s="3">
         <v>13000</v>
       </c>
       <c r="T83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="U83" s="3">
         <v>14000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13000</v>
-      </c>
-      <c r="V83" s="3">
-        <v>14000</v>
       </c>
       <c r="W83" s="3">
         <v>14000</v>
       </c>
       <c r="X83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="Y83" s="3">
         <v>15000</v>
       </c>
       <c r="Z83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="AA83" s="3">
         <v>16000</v>
@@ -8476,43 +8674,46 @@
         <v>16000</v>
       </c>
       <c r="AC83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AD83" s="3">
         <v>17000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>19000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>23000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>22000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>21000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>20000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>570000</v>
+      </c>
+      <c r="E89" s="3">
         <v>720000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>562000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>638000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>703000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>748000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>616000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>504000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>520000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>828000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>501000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>436000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>512000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>737000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>608000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>645000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>643000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>669000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>603000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>82000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>367000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>758000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>438000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>212000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>160000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>466000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>227000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>287000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>359000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>514000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>136000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>218000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>360000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>379000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>233000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>282000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>296000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,82 +9468,83 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-24000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-6000</v>
       </c>
       <c r="AB91" s="3">
         <v>-6000</v>
@@ -9333,40 +9553,43 @@
         <v>-6000</v>
       </c>
       <c r="AD91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AH91" s="3">
         <v>-38000</v>
       </c>
       <c r="AI91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-975000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-559000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>88000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-555000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-553000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>40000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-249000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-306000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-679000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-909000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>51000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-440000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-641000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-302000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-129000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-631000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-395000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-610000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>408000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-298000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-882000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-612000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1087000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-165000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-293000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>289000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-257000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>489000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>354000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,124 +9987,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E96" s="3">
         <v>125000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>125600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>125900</v>
       </c>
-      <c r="G96" s="3">
-        <v>119600</v>
-      </c>
       <c r="H96" s="3">
+        <v>119000</v>
+      </c>
+      <c r="I96" s="3">
         <v>120000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>119000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>667000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>114000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>442800</v>
       </c>
-      <c r="M96" s="3" t="s">
+      <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>445000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-108000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-109000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-108000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-657000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-104000</v>
       </c>
       <c r="U96" s="3">
         <v>-104000</v>
       </c>
       <c r="V96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-100000</v>
       </c>
       <c r="X96" s="3">
         <v>-100000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-101000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-649000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-95000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-96000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-95000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AF96" s="3">
         <v>-95000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-626000</v>
+      </c>
+      <c r="E100" s="3">
         <v>369000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-125000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-722000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-119000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-120000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-689000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-189000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-359000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>280000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-480000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-108000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-138000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-98000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-688000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-103000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-104000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-120000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-321000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-101000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-101000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-675000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-101000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-123000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-96000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-134000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-15000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AK101" s="3">
         <v>4000</v>
       </c>
       <c r="AL101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E102" s="3">
         <v>110000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-110000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>81000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-34000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>64000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-140000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>127000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-125000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-57000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>199000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-175000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-89000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>163000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-126000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>169000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-23000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-144000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-271000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>615000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>69000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>48000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-87000</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>22000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>72000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>58000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>28000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>CNA</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3991000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3828000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3817000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3717000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3627000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3689000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3618000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3519000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3444000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3507000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3336000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3304000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3152000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3111000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2957000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2926000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2885000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3054000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2959000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3029000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2866000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2931000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2820000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2766000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2291000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2787000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2699000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2616000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2709000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2625000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2574000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2541000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2403000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2368000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2332000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2415000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2451000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2965000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2625000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2515000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2554000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2498000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2492000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2476000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2317000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2251000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2246000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2252000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2182000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2032000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>389000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>383000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>374000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>344000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>359000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>368000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>357000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>359000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>364000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>360000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>342000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>344000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>358000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>345000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>338000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>342000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>343000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>337000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>359000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>296000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>307000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>309000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>312000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>305000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>309000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1026000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1203000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1302000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1163000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1129000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1197000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1142000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1202000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1193000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1261000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1084000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1122000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1120000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2722000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2574000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2552000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2541000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2695000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2591000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2672000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2507000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2567000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2460000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2424000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1947000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2429000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2354000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2278000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2367000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2072000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2288000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2215000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2245000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2146000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2094000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2056000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2027000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2106000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2137000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,8 +1520,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1518,8 +1538,8 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1536,92 +1556,95 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>10000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>14000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>14000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>12000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>6000</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>5000</v>
       </c>
       <c r="AK14" s="3">
         <v>5000</v>
       </c>
       <c r="AL14" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="AM14" s="3">
         <v>2000</v>
       </c>
       <c r="AN14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AO14" s="3">
         <v>25000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E15" s="3">
         <v>17000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>18000</v>
       </c>
       <c r="F15" s="3">
         <v>18000</v>
       </c>
       <c r="G15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="H15" s="3">
         <v>17000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>18000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>29000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>16000</v>
       </c>
       <c r="N15" s="3">
         <v>16000</v>
       </c>
       <c r="O15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="P15" s="3">
         <v>12000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3691000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3414000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3268000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3306000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3246000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3636000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3225000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3083000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2982000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3013000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2976000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2912000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2753000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2800000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2980000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2671000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2502000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2696000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2617000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2538000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2460000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2425000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2538000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2553000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2349000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2421000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2540000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2240000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2256000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2189000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2160000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2006000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2175000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1958000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1946000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2058000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1937000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300000</v>
+      </c>
+      <c r="E18" s="3">
         <v>414000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>549000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>411000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>381000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>53000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>393000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>436000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>462000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>494000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>360000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>392000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>399000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>311000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>255000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>383000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>358000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>342000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>491000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>406000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>506000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>282000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>213000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>366000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>159000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>376000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>453000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-80000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>436000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>365000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>381000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>447000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>228000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>410000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>386000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>357000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>514000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,8 +2093,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2137,141 +2171,147 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>320000</v>
+      </c>
+      <c r="E21" s="3">
         <v>431000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>567000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>429000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>398000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>69000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>410000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>454000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>478000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>523000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>376000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>408000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>411000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>324000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>267000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>396000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>371000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>356000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>504000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>420000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>520000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>297000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>228000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>382000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>175000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>393000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>472000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-60000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>454000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>386000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>401000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>469000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>251000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>432000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>407000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>377000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>36000</v>
+        <v>33000</v>
       </c>
       <c r="E22" s="3">
         <v>36000</v>
       </c>
       <c r="F22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="G22" s="3">
         <v>31000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>32000</v>
       </c>
       <c r="H22" s="3">
         <v>32000</v>
@@ -2280,22 +2320,22 @@
         <v>32000</v>
       </c>
       <c r="J22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="K22" s="3">
         <v>34000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>34000</v>
       </c>
       <c r="M22" s="3">
         <v>34000</v>
       </c>
       <c r="N22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="O22" s="3">
         <v>31000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>28000</v>
       </c>
       <c r="P22" s="3">
         <v>28000</v>
@@ -2316,19 +2356,19 @@
         <v>28000</v>
       </c>
       <c r="V22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="W22" s="3">
         <v>29000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>28000</v>
       </c>
       <c r="X22" s="3">
         <v>28000</v>
       </c>
       <c r="Y22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>32000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>31000</v>
       </c>
       <c r="AA22" s="3">
         <v>31000</v>
@@ -2337,10 +2377,10 @@
         <v>31000</v>
       </c>
       <c r="AC22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>32000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>34000</v>
       </c>
       <c r="AE22" s="3">
         <v>34000</v>
@@ -2352,269 +2392,278 @@
         <v>34000</v>
       </c>
       <c r="AH22" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="AI22" s="3">
         <v>35000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AK22" s="3">
         <v>37000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>41000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>40000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>43000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>40000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E23" s="3">
         <v>378000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>513000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>380000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>349000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>361000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>402000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>427000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>460000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>326000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>361000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>371000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>283000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-51000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>227000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>355000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>330000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>314000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>462000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>378000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>478000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>250000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>182000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-89000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>335000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>127000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>342000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>419000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-114000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>402000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>330000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>346000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>410000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>187000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>370000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>343000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>317000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E24" s="3">
         <v>76000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>110000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>81000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>75000</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>78000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>85000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>89000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>93000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>68000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>78000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>74000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>44000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>60000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>64000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>58000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>94000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>66000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>91000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>37000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>31000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>62000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>20000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>64000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>77000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>66000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>60000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>104000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>43000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>98000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>83000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>76000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E26" s="3">
         <v>302000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>403000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>299000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>274000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>283000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>317000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>338000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>367000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>258000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>283000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>297000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>239000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-42000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>190000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>295000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>266000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>256000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>368000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>312000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>387000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>213000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>151000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>273000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>107000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>278000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>342000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-84000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>336000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>270000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>291000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>306000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>144000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>272000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>260000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>241000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E27" s="3">
         <v>302000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>403000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>299000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>274000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>283000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>317000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>338000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>367000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>258000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>283000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>297000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>239000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-42000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>190000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>295000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>266000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>256000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>368000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>312000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>387000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>213000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>151000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>273000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>107000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>278000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>342000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>336000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>270000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>291000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>306000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>144000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>272000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>260000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>241000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3172,8 +3233,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3190,26 +3251,29 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-83000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,8 +3557,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3565,127 +3635,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E33" s="3">
         <v>302000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>403000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>299000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>274000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>283000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>317000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>338000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>367000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>258000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>283000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>297000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>239000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-42000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>190000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>295000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>266000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>256000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>368000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>312000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>387000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>213000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>151000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>273000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>107000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>278000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>342000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>336000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>270000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>291000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>223000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>144000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>272000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>260000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>241000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E35" s="3">
         <v>302000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>403000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>299000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>274000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>283000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>317000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>338000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>367000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>258000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>283000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>297000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>239000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-42000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>190000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>295000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>266000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>256000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>368000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>312000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>387000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>213000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>151000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>273000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>107000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>278000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>342000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>336000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>270000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>291000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>223000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>144000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>272000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>260000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>241000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,169 +4218,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>522000</v>
+      </c>
+      <c r="E41" s="3">
         <v>425000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>483000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>373000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>483000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>472000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>456000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>375000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>409000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>345000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>485000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>358000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>483000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>475000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>503000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>560000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>361000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>536000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>625000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>462000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>588000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>419000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>442000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>586000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>857000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>242000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>340000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>271000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>223000</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>310000</v>
       </c>
       <c r="AG41" s="3">
         <v>310000</v>
       </c>
       <c r="AH41" s="3">
+        <v>310000</v>
+      </c>
+      <c r="AI41" s="3">
         <v>288000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>282000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>355000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>283000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>225000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>299000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>271000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1499000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2320000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2258000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1743000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1586000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2088000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1900000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1751000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1996000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2165000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1961000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1924000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1181000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4370,127 +4460,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3720000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3739000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3666000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4062000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3703000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3671000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3494000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3816000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3432000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3442000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3211000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3521000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3126000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3158000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2986000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3210000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2892000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2945000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2799000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2954000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2652000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2607000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2527000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2755000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2502000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2481000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2504000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2690000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2476000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2365000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2400000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2642000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2414000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2191000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2281000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,50 +4704,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6874000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6861000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6925000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6878000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6731000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6502000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6258000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6105000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6021000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5856000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5888000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6005000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5899000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4727,50 +4826,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12615000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13345000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13332000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13056000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12503000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12733000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12108000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12047000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11858000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11808000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11545000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11808000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10689000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4846,299 +4948,308 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46948000</v>
+      </c>
+      <c r="E47" s="3">
         <v>47048000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47223000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46265000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45334000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>44375000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45792000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43508000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43649000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>43362000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>40691000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41502000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>41836000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>43177000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>42137000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>44280000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>47106000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>50328000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>50236000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>50265000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>48671000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>50293000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>49006000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>47757000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>44086000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>47744000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>47535000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>45639000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>44486000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>44929000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>45152000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>45535000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>46870000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>46747000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>46268000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>45279000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>45420000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>46980000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E48" s="3">
         <v>430000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>283000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>297000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>291000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>453000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>258000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>259000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>256000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>393000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>257000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>246000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>232000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>226000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>229000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>227000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>225000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>226000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>234000</v>
       </c>
       <c r="V48" s="3">
         <v>234000</v>
       </c>
       <c r="W48" s="3">
+        <v>234000</v>
+      </c>
+      <c r="X48" s="3">
         <v>244000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>451000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>256000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>264000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>271000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>502000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>516000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>525000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>547000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>324000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>332000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>347000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>346000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>326000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>325000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>336000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>324000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>310000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1155000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1134000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1133000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1169000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1145000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1104000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1090000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1094000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1073000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1120000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1025000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1031000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>997000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>144000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>142000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>145000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>147000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>148000</v>
       </c>
       <c r="U49" s="3">
         <v>148000</v>
@@ -5153,58 +5264,61 @@
         <v>148000</v>
       </c>
       <c r="Y49" s="3">
+        <v>148000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>146000</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>145000</v>
       </c>
       <c r="AA49" s="3">
         <v>145000</v>
       </c>
       <c r="AB49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>147000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>145000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>146000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>147000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>146000</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>147000</v>
       </c>
       <c r="AH49" s="3">
         <v>147000</v>
       </c>
       <c r="AI49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>149000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>148000</v>
-      </c>
-      <c r="AK49" s="3">
-        <v>147000</v>
       </c>
       <c r="AL49" s="3">
         <v>147000</v>
       </c>
       <c r="AM49" s="3">
+        <v>147000</v>
+      </c>
+      <c r="AN49" s="3">
         <v>146000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>145000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2798000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2612000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2805000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2909000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2732000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2433000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2779000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2761000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2647000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2316000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2474000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2602000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2467000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1251000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1298000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>927000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>547000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>142000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>135000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>121000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>197000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>66000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>144000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>195000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>518000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>199000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>190000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>106000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>217000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>392000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>314000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>296000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>238000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>137000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>141000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>166000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>267000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>379000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68559000</v>
+      </c>
+      <c r="E54" s="3">
         <v>69443000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>69756000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68936000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>67326000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66492000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>67356000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>65194000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65075000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>64711000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>61952000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63088000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>62055000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>61000000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>60215000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>62229000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>63792000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>66639000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66522000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66207000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>63713000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64026000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62775000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>62095000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>58405000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60612000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60450000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>59963000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>58477000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>57152000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>57259000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>57858000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>57649000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>56567000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>56582000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>56205000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>55201000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>55233000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>56859000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,50 +6014,51 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27381000</v>
+      </c>
+      <c r="E57" s="3">
         <v>27069000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26911000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26203000</v>
       </c>
-      <c r="G57" s="3">
-        <v>25581000</v>
-      </c>
       <c r="H57" s="3">
+        <v>25989000</v>
+      </c>
+      <c r="I57" s="3">
         <v>25401000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24558000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23974000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23588000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23721000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22836000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22802000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22409000</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -6003,16 +6134,19 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>34000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>500000</v>
       </c>
       <c r="F58" s="3">
         <v>500000</v>
@@ -6021,7 +6155,7 @@
         <v>500000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -6030,25 +6164,25 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>550000</v>
       </c>
       <c r="M58" s="3">
+        <v>550000</v>
+      </c>
+      <c r="N58" s="3">
         <v>793000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>792000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>243000</v>
       </c>
       <c r="P58" s="3">
         <v>243000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
+      <c r="Q58" s="3">
+        <v>243000</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -6065,8 +6199,8 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -6099,13 +6233,13 @@
         <v>0</v>
       </c>
       <c r="AH58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3">
         <v>30000</v>
       </c>
       <c r="AJ58" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="AK58" s="3">
         <v>150000</v>
@@ -6117,174 +6251,180 @@
         <v>150000</v>
       </c>
       <c r="AN58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8046000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9035000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7978000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8690000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8604000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8746000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7659000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8209000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8146000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6934000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7689000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7878000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7781000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19854000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16649000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17215000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17880000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19245000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18775000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18877000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18091000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18716000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17998000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17592000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16479000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17195000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17217000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16486000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15808000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14780000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14894000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>15077000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>15039000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>15208000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>15100000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>14931000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>14403000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>14088000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>15081000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35427000</v>
+      </c>
+      <c r="E60" s="3">
         <v>36171000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35389000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35393000</v>
       </c>
-      <c r="G60" s="3">
-        <v>34685000</v>
-      </c>
       <c r="H60" s="3">
+        <v>35093000</v>
+      </c>
+      <c r="I60" s="3">
         <v>34177000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32217000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32183000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32284000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31233000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31318000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31472000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30433000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6360,169 +6500,175 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2972000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3155000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2970000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2475000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2474000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3212000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2972000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2971000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2970000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2696000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2480000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2384000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2539000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2538000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2780000</v>
       </c>
       <c r="R61" s="3">
         <v>2780000</v>
       </c>
       <c r="S61" s="3">
-        <v>2779000</v>
+        <v>2780000</v>
       </c>
       <c r="T61" s="3">
         <v>2779000</v>
       </c>
       <c r="U61" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="V61" s="3">
         <v>2778000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>2777000</v>
       </c>
       <c r="W61" s="3">
         <v>2777000</v>
       </c>
       <c r="X61" s="3">
-        <v>2776000</v>
+        <v>2777000</v>
       </c>
       <c r="Y61" s="3">
         <v>2776000</v>
       </c>
       <c r="Z61" s="3">
-        <v>2680000</v>
+        <v>2776000</v>
       </c>
       <c r="AA61" s="3">
         <v>2680000</v>
       </c>
       <c r="AB61" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>2679000</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>2678000</v>
       </c>
       <c r="AD61" s="3">
         <v>2678000</v>
       </c>
       <c r="AE61" s="3">
+        <v>2678000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>2681000</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>2680000</v>
       </c>
       <c r="AG61" s="3">
         <v>2680000</v>
       </c>
       <c r="AH61" s="3">
-        <v>2679000</v>
+        <v>2680000</v>
       </c>
       <c r="AI61" s="3">
         <v>2679000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>2679000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>2708000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2707000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2560000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2710000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2709000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15727000</v>
+      </c>
+      <c r="E62" s="3">
         <v>15718000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16181000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16786000</v>
       </c>
-      <c r="G62" s="3">
-        <v>16500000</v>
-      </c>
       <c r="H62" s="3">
+        <v>16092000</v>
+      </c>
+      <c r="I62" s="3">
         <v>15415000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17215000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16343000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16614000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16144000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15755000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16671000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16906000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6598,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57702000</v>
+      </c>
+      <c r="E66" s="3">
         <v>57822000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>58434000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>58275000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57047000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>55979000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>56598000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55320000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55413000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54818000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53389000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54362000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53388000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52452000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>52121000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52717000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>52975000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>53830000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>53858000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>53539000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51624000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51319000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>50754000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50450000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>48043000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>48397000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>48327000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>47876000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>47022000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>45935000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>45749000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>46443000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>46224000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>44323000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>44413000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>44177000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>43508000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>43264000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>44664000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9448000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9915000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9739000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9460000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9287000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9686000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9785000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9623000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9425000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9755000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9503000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9359000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9191000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9336000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9433000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9415000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9319000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9663000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9500000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9348000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9084000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9081000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8796000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8683000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8634000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9348000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9171000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9159000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8976000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9277000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9456000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9216000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9028000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9414000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9273000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9006000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9359000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9185000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10857000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11621000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11322000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10661000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10279000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10513000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10758000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9874000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9662000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9893000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8563000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8726000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8667000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8548000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8094000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9512000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10817000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12809000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12664000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12668000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12089000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12707000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12021000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11645000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10362000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12215000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12123000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12087000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11455000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11217000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11510000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11415000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11425000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12244000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12169000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12028000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11693000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11969000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>12195000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E81" s="3">
         <v>302000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>403000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>299000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>274000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>283000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>317000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>338000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>367000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>258000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>283000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>297000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>239000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-42000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>190000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>295000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>266000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>256000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>368000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>312000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>387000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>213000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>151000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>273000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>107000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>278000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>342000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>336000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>270000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>291000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>223000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>144000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>272000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>260000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>241000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,46 +8791,47 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E83" s="3">
         <v>16000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>16000</v>
       </c>
       <c r="J83" s="3">
         <v>16000</v>
       </c>
       <c r="K83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="L83" s="3">
         <v>12000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>13000</v>
       </c>
       <c r="M83" s="3">
         <v>13000</v>
       </c>
       <c r="N83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O83" s="3">
         <v>12000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>13000</v>
       </c>
       <c r="P83" s="3">
         <v>13000</v>
@@ -8641,34 +8840,34 @@
         <v>13000</v>
       </c>
       <c r="R83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="S83" s="3">
         <v>12000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>13000</v>
       </c>
       <c r="T83" s="3">
         <v>13000</v>
       </c>
       <c r="U83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="V83" s="3">
         <v>14000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>14000</v>
       </c>
       <c r="X83" s="3">
         <v>14000</v>
       </c>
       <c r="Y83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="Z83" s="3">
         <v>15000</v>
       </c>
       <c r="AA83" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="AB83" s="3">
         <v>16000</v>
@@ -8677,43 +8876,46 @@
         <v>16000</v>
       </c>
       <c r="AD83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AE83" s="3">
         <v>17000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>19000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>18000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>23000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>22000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>21000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>20000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E89" s="3">
         <v>570000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>720000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>562000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>638000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>703000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>748000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>616000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>504000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>520000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>828000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>501000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>436000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>512000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>737000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>608000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>645000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>643000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>669000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>603000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>82000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>367000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>758000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>438000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>212000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>160000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>466000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>227000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>287000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>359000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>514000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>136000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>360000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>379000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>233000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>282000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>296000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,85 +9689,86 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-6000</v>
       </c>
       <c r="AC91" s="3">
         <v>-6000</v>
@@ -9556,40 +9777,43 @@
         <v>-6000</v>
       </c>
       <c r="AE91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-38000</v>
       </c>
       <c r="AI91" s="3">
         <v>-38000</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>444000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-975000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-559000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>88000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-555000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-553000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>40000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-249000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-306000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-679000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-909000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>51000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-440000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-641000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-302000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-129000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-631000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-395000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-610000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>408000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-298000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-882000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-612000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1087000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-165000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-293000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>289000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-257000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>489000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-206000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-329000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>354000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-437000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,127 +10221,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E96" s="3">
         <v>125200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>125000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>125600</v>
       </c>
-      <c r="G96" s="3">
-        <v>125900</v>
-      </c>
       <c r="H96" s="3">
+        <v>673000</v>
+      </c>
+      <c r="I96" s="3">
         <v>119000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>120000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>119000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>667000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>114000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>442800</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>445000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-108000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-109000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-108000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-657000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-104000</v>
       </c>
       <c r="V96" s="3">
         <v>-104000</v>
       </c>
       <c r="W96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-100000</v>
       </c>
       <c r="Y96" s="3">
         <v>-100000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-101000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-649000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-95000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-96000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-95000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-643000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AG96" s="3">
         <v>-95000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-82000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-624000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-85000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-67000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-736000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-626000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>369000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-125000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-722000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-119000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-120000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-689000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-189000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-359000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-18000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>280000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-480000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-108000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-138000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-98000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-688000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-103000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-104000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-120000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-321000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-101000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-101000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-675000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-101000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-123000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-665000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-96000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-134000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-781000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-82000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>4000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-67000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-13000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-15000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-15000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>9000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AL101" s="3">
         <v>4000</v>
       </c>
       <c r="AM101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AN101" s="3">
         <v>1000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-58000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>110000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-110000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>81000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-34000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>64000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-140000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>127000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-125000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-57000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>199000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-175000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-89000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>163000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-126000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>169000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-144000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-271000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>615000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-98000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>69000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>48000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-87000</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>22000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>72000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>58000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>28000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1000</v>
       </c>
     </row>
